--- a/data/output/sim_gridrnd/REL2/group_520_40/results/REL2_G8_results_summary.xlsx
+++ b/data/output/sim_gridrnd/REL2/group_520_40/results/REL2_G8_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,630 +466,718 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S04_G8_519_38_REL2</t>
+          <t>S01_G8_521_41_REL2</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C2" t="n">
-        <v>38</v>
+        <v>60.78576723498888</v>
       </c>
       <c r="D2" t="n">
-        <v>56.33802816901409</v>
+        <v>41</v>
       </c>
       <c r="E2" t="n">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F2" t="n">
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>80.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>525.9290578440111</v>
-      </c>
-      <c r="J2" t="n">
-        <v>26.21520271067261</v>
-      </c>
-      <c r="K2" t="n">
-        <v>521.5777599397379</v>
-      </c>
-      <c r="L2" t="n">
-        <v>35.56007002437188</v>
-      </c>
-      <c r="M2" t="n">
-        <v>522.9173575462657</v>
-      </c>
-      <c r="N2" t="n">
-        <v>33.68839973178869</v>
-      </c>
-      <c r="O2" t="n">
-        <v>513.6739314215901</v>
-      </c>
-      <c r="P2" t="n">
-        <v>34.0499310260038</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>512.974166056224</v>
-      </c>
       <c r="R2" t="n">
-        <v>41.0893404228593</v>
+        <v>503.78</v>
       </c>
       <c r="S2" t="n">
-        <v>512.606227280847</v>
+        <v>45.3</v>
       </c>
       <c r="T2" t="n">
-        <v>40.98228205609068</v>
+        <v>502.83</v>
       </c>
       <c r="U2" t="n">
-        <v>512.4971507200521</v>
+        <v>53.73</v>
       </c>
       <c r="V2" t="n">
-        <v>38.21321660144392</v>
+        <v>520.33</v>
       </c>
       <c r="W2" t="n">
-        <v>513.3840360004521</v>
+        <v>54.5</v>
       </c>
       <c r="X2" t="n">
-        <v>38.43182909726263</v>
+        <v>527.26</v>
       </c>
       <c r="Y2" t="n">
-        <v>515.2314727796854</v>
+        <v>50.01</v>
       </c>
       <c r="Z2" t="n">
-        <v>40.69928903744491</v>
+        <v>521.73</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>57.36</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>530.27</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>56.38</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>529.79</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>53.84</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>529.49</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>53.12</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>529.2</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>53.86</v>
       </c>
       <c r="AJ2" t="n">
-        <v>505.325</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>509.4</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>511.2625</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>512.1900000000001</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>511.9666666666666</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>511.7214285714286</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>511.6</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>511.5611111111111</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>511.79</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>70.48701564827383</v>
+        <v>511.225</v>
       </c>
       <c r="AT2" t="n">
-        <v>61.71823069401779</v>
+        <v>507.6833333333333</v>
       </c>
       <c r="AU2" t="n">
-        <v>57.46841387884304</v>
+        <v>508.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>53.88630531034764</v>
+        <v>512.0599999999999</v>
       </c>
       <c r="AW2" t="n">
-        <v>51.34977009577442</v>
+        <v>513.8083333333333</v>
       </c>
       <c r="AX2" t="n">
-        <v>50.27127379913657</v>
+        <v>515.4571428571429</v>
       </c>
       <c r="AY2" t="n">
-        <v>49.23796807342886</v>
+        <v>516.70625</v>
       </c>
       <c r="AZ2" t="n">
-        <v>48.03519125355318</v>
+        <v>517.6166666666667</v>
       </c>
       <c r="BA2" t="n">
-        <v>47.31443648612968</v>
+        <v>518.295</v>
       </c>
       <c r="BB2" t="n">
-        <v>334</v>
+        <v>84.63465232988199</v>
       </c>
       <c r="BC2" t="n">
-        <v>334</v>
+        <v>77.16940059951799</v>
       </c>
       <c r="BD2" t="n">
-        <v>334</v>
+        <v>73.69165488710374</v>
       </c>
       <c r="BE2" t="n">
-        <v>334</v>
+        <v>71.10370173204768</v>
       </c>
       <c r="BF2" t="n">
-        <v>334</v>
+        <v>69.25692454348679</v>
       </c>
       <c r="BG2" t="n">
-        <v>334</v>
+        <v>67.68143567252307</v>
       </c>
       <c r="BH2" t="n">
-        <v>334</v>
+        <v>67.7661970375902</v>
       </c>
       <c r="BI2" t="n">
-        <v>334</v>
+        <v>67.02713173699803</v>
       </c>
       <c r="BJ2" t="n">
-        <v>334</v>
+        <v>66.27479139914361</v>
       </c>
       <c r="BK2" t="n">
-        <v>669</v>
+        <v>332</v>
       </c>
       <c r="BL2" t="n">
-        <v>669</v>
+        <v>332</v>
       </c>
       <c r="BM2" t="n">
-        <v>669</v>
+        <v>332</v>
       </c>
       <c r="BN2" t="n">
-        <v>669</v>
+        <v>332</v>
       </c>
       <c r="BO2" t="n">
-        <v>669</v>
+        <v>332</v>
       </c>
       <c r="BP2" t="n">
-        <v>669</v>
+        <v>332</v>
       </c>
       <c r="BQ2" t="n">
-        <v>669</v>
+        <v>332</v>
       </c>
       <c r="BR2" t="n">
-        <v>669</v>
+        <v>332</v>
       </c>
       <c r="BS2" t="n">
-        <v>669</v>
+        <v>332</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.1428571428571428</v>
+        <v>669</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.875</v>
+        <v>669</v>
       </c>
       <c r="BV2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD2" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="BW2" t="n">
-        <v>0.9032258064516129</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0.8918918918918919</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0.9069767441860465</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0.9565217391304348</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0.8679245283018868</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>0.8166666666666667</v>
+      <c r="CE2" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>0.8275862068965517</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.717948717948718</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0.6222222222222222</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>0.509090909090909</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>529.2</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>53.86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S01_G8_521_41_REL2</t>
+          <t>S02_G8_521_42_REL2</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>521</v>
       </c>
       <c r="C3" t="n">
-        <v>41</v>
+        <v>62.26834692364714</v>
       </c>
       <c r="D3" t="n">
-        <v>60.78576723498888</v>
+        <v>42</v>
       </c>
       <c r="E3" t="n">
         <v>521</v>
@@ -1098,228 +1186,261 @@
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>503.7843511011167</v>
-      </c>
-      <c r="J3" t="n">
-        <v>45.30238697618251</v>
-      </c>
-      <c r="K3" t="n">
-        <v>502.8257099822153</v>
-      </c>
-      <c r="L3" t="n">
-        <v>53.72865568505642</v>
-      </c>
-      <c r="M3" t="n">
-        <v>520.3338278376422</v>
-      </c>
-      <c r="N3" t="n">
-        <v>54.50244530055637</v>
-      </c>
-      <c r="O3" t="n">
-        <v>527.2610118044427</v>
-      </c>
-      <c r="P3" t="n">
-        <v>50.01081863284178</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>521.7348621180651</v>
-      </c>
       <c r="R3" t="n">
-        <v>57.35506525218118</v>
+        <v>514.09</v>
       </c>
       <c r="S3" t="n">
-        <v>530.2708747128182</v>
+        <v>32.58</v>
       </c>
       <c r="T3" t="n">
-        <v>56.37681244464856</v>
+        <v>509.48</v>
       </c>
       <c r="U3" t="n">
-        <v>529.7905666226003</v>
+        <v>37.15</v>
       </c>
       <c r="V3" t="n">
-        <v>53.83820514130487</v>
+        <v>513.51</v>
       </c>
       <c r="W3" t="n">
-        <v>529.4895334729958</v>
+        <v>35.68</v>
       </c>
       <c r="X3" t="n">
-        <v>53.11881372584485</v>
+        <v>510.75</v>
       </c>
       <c r="Y3" t="n">
-        <v>529.2009644312412</v>
+        <v>35.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>53.85516075709425</v>
+        <v>513.35</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>37.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>512.24</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>40.43</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>511.07</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>43.42</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>513.8099999999999</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>44.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>514.9299999999999</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>44.44</v>
       </c>
       <c r="AJ3" t="n">
-        <v>511.225</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>507.6833333333333</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>508.8</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>512.0599999999999</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>513.8083333333333</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>515.4571428571429</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>516.70625</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>517.6166666666667</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>518.295</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>84.63465232988199</v>
+        <v>509.775</v>
       </c>
       <c r="AT3" t="n">
-        <v>77.16940059951799</v>
+        <v>510.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>73.69165488710374</v>
+        <v>511.3</v>
       </c>
       <c r="AV3" t="n">
-        <v>71.10370173204768</v>
+        <v>511.07</v>
       </c>
       <c r="AW3" t="n">
-        <v>69.25692454348679</v>
+        <v>510.375</v>
       </c>
       <c r="AX3" t="n">
-        <v>67.68143567252307</v>
+        <v>509.8071428571429</v>
       </c>
       <c r="AY3" t="n">
-        <v>67.7661970375902</v>
+        <v>510.2</v>
       </c>
       <c r="AZ3" t="n">
-        <v>67.02713173699803</v>
+        <v>510.8222222222222</v>
       </c>
       <c r="BA3" t="n">
-        <v>66.27479139914361</v>
+        <v>512.3200000000001</v>
       </c>
       <c r="BB3" t="n">
+        <v>73.17461564641116</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>64.605082359414</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>59.73993639099393</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>56.72605309732028</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>54.38383070055535</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>52.58162313809583</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>51.16404987879673</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>51.66302735091826</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>52.14400828474927</v>
+      </c>
+      <c r="BK3" t="n">
         <v>332</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BL3" t="n">
         <v>332</v>
       </c>
-      <c r="BD3" t="n">
+      <c r="BM3" t="n">
         <v>332</v>
       </c>
-      <c r="BE3" t="n">
+      <c r="BN3" t="n">
         <v>332</v>
       </c>
-      <c r="BF3" t="n">
+      <c r="BO3" t="n">
         <v>332</v>
       </c>
-      <c r="BG3" t="n">
+      <c r="BP3" t="n">
         <v>332</v>
       </c>
-      <c r="BH3" t="n">
+      <c r="BQ3" t="n">
         <v>332</v>
       </c>
-      <c r="BI3" t="n">
+      <c r="BR3" t="n">
         <v>332</v>
       </c>
-      <c r="BJ3" t="n">
+      <c r="BS3" t="n">
         <v>332</v>
       </c>
-      <c r="BK3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>669</v>
-      </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.8461538461538461</v>
+        <v>669</v>
       </c>
       <c r="BV3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0.9111111111111111</v>
+      </c>
+      <c r="CJ3" t="n">
         <v>0.9375</v>
       </c>
-      <c r="BW3" t="n">
-        <v>0.9090909090909091</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>0.8275862068965517</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0.717948717948718</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0.6222222222222222</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>0.509090909090909</v>
+      <c r="CK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>514.9299999999999</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>44.44</v>
       </c>
     </row>
     <row r="4">
@@ -1332,10 +1453,10 @@
         <v>522</v>
       </c>
       <c r="C4" t="n">
+        <v>57.82060785767235</v>
+      </c>
+      <c r="D4" t="n">
         <v>39</v>
-      </c>
-      <c r="D4" t="n">
-        <v>57.82060785767235</v>
       </c>
       <c r="E4" t="n">
         <v>522</v>
@@ -1344,1458 +1465,1656 @@
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>507.4759045368603</v>
-      </c>
-      <c r="J4" t="n">
-        <v>32.83163511249123</v>
-      </c>
-      <c r="K4" t="n">
-        <v>515.3547766172437</v>
-      </c>
-      <c r="L4" t="n">
-        <v>35.25830025424282</v>
-      </c>
-      <c r="M4" t="n">
-        <v>518.3321615582394</v>
-      </c>
-      <c r="N4" t="n">
-        <v>44.11043585202199</v>
-      </c>
-      <c r="O4" t="n">
-        <v>522.3471392852369</v>
-      </c>
-      <c r="P4" t="n">
-        <v>48.70472208654301</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>522.7723898695315</v>
-      </c>
       <c r="R4" t="n">
-        <v>49.17369858206118</v>
+        <v>507.48</v>
       </c>
       <c r="S4" t="n">
-        <v>520.8554044295427</v>
+        <v>32.83</v>
       </c>
       <c r="T4" t="n">
-        <v>54.05358443974919</v>
+        <v>515.35</v>
       </c>
       <c r="U4" t="n">
-        <v>519.8126595070547</v>
+        <v>35.26</v>
       </c>
       <c r="V4" t="n">
-        <v>49.30371122151448</v>
+        <v>518.33</v>
       </c>
       <c r="W4" t="n">
-        <v>518.6972806614158</v>
+        <v>44.11</v>
       </c>
       <c r="X4" t="n">
-        <v>48.39182009738008</v>
+        <v>522.35</v>
       </c>
       <c r="Y4" t="n">
-        <v>520.9386593629753</v>
+        <v>48.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>48.40104132093828</v>
+        <v>522.77</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>49.17</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>520.86</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>54.05</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>519.8099999999999</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>49.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>518.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>48.39</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>520.9400000000001</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>48.4</v>
       </c>
       <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
         <v>521.45</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AT4" t="n">
         <v>513</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AU4" t="n">
         <v>514.7</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AV4" t="n">
         <v>516.3200000000001</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AW4" t="n">
         <v>517.6833333333333</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AX4" t="n">
         <v>517.4571428571429</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AY4" t="n">
         <v>515.575</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AZ4" t="n">
         <v>514.0888888888888</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="BA4" t="n">
         <v>514.595</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="BB4" t="n">
         <v>85.10550804736437</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="BC4" t="n">
         <v>72.69548358277379</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="BD4" t="n">
         <v>68.03241874283171</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="BE4" t="n">
         <v>65.55148816007154</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="BF4" t="n">
         <v>64.24613909713867</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="BG4" t="n">
         <v>64.73698119849178</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="BH4" t="n">
         <v>64.32520404165074</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BI4" t="n">
         <v>62.89614799094429</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="BJ4" t="n">
         <v>61.67577299880399</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BK4" t="n">
         <v>328</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BL4" t="n">
         <v>328</v>
       </c>
-      <c r="BD4" t="n">
+      <c r="BM4" t="n">
         <v>328</v>
       </c>
-      <c r="BE4" t="n">
+      <c r="BN4" t="n">
         <v>328</v>
       </c>
-      <c r="BF4" t="n">
+      <c r="BO4" t="n">
         <v>328</v>
       </c>
-      <c r="BG4" t="n">
+      <c r="BP4" t="n">
         <v>328</v>
       </c>
-      <c r="BH4" t="n">
+      <c r="BQ4" t="n">
         <v>328</v>
       </c>
-      <c r="BI4" t="n">
+      <c r="BR4" t="n">
         <v>328</v>
       </c>
-      <c r="BJ4" t="n">
+      <c r="BS4" t="n">
         <v>328</v>
       </c>
-      <c r="BK4" t="n">
+      <c r="BT4" t="n">
         <v>675</v>
       </c>
-      <c r="BL4" t="n">
+      <c r="BU4" t="n">
         <v>675</v>
       </c>
-      <c r="BM4" t="n">
+      <c r="BV4" t="n">
         <v>675</v>
       </c>
-      <c r="BN4" t="n">
+      <c r="BW4" t="n">
         <v>675</v>
       </c>
-      <c r="BO4" t="n">
+      <c r="BX4" t="n">
         <v>675</v>
       </c>
-      <c r="BP4" t="n">
+      <c r="BY4" t="n">
         <v>675</v>
       </c>
-      <c r="BQ4" t="n">
+      <c r="BZ4" t="n">
         <v>675</v>
       </c>
-      <c r="BR4" t="n">
+      <c r="CA4" t="n">
         <v>675</v>
       </c>
-      <c r="BS4" t="n">
+      <c r="CB4" t="n">
         <v>675</v>
       </c>
-      <c r="BT4" t="n">
+      <c r="CC4" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BU4" t="n">
+      <c r="CD4" t="n">
         <v>0.3636363636363636</v>
       </c>
-      <c r="BV4" t="n">
+      <c r="CE4" t="n">
         <v>0.4705882352941176</v>
       </c>
-      <c r="BW4" t="n">
+      <c r="CF4" t="n">
         <v>0.5454545454545454</v>
       </c>
-      <c r="BX4" t="n">
+      <c r="CG4" t="n">
         <v>0.7037037037037037</v>
       </c>
-      <c r="BY4" t="n">
+      <c r="CH4" t="n">
         <v>0.896551724137931</v>
       </c>
-      <c r="BZ4" t="n">
+      <c r="CI4" t="n">
         <v>0.896551724137931</v>
       </c>
-      <c r="CA4" t="n">
+      <c r="CJ4" t="n">
         <v>0.8125</v>
       </c>
-      <c r="CB4" t="n">
+      <c r="CK4" t="n">
         <v>0.8125</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>520.9400000000001</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>48.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S02_G8_521_42_REL2</t>
+          <t>S04_G8_519_38_REL2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C5" t="n">
-        <v>42</v>
+        <v>56.33802816901409</v>
       </c>
       <c r="D5" t="n">
-        <v>62.26834692364714</v>
+        <v>38</v>
       </c>
       <c r="E5" t="n">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F5" t="n">
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>514.0920925996317</v>
-      </c>
-      <c r="J5" t="n">
-        <v>32.58247486495867</v>
-      </c>
-      <c r="K5" t="n">
-        <v>509.4758038572835</v>
-      </c>
-      <c r="L5" t="n">
-        <v>37.15425089710332</v>
-      </c>
-      <c r="M5" t="n">
-        <v>513.5130039430967</v>
-      </c>
-      <c r="N5" t="n">
-        <v>35.67617532152875</v>
-      </c>
-      <c r="O5" t="n">
-        <v>510.7527587710555</v>
-      </c>
-      <c r="P5" t="n">
-        <v>35.29831691086449</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>513.3455083312512</v>
-      </c>
       <c r="R5" t="n">
-        <v>37.89610095548687</v>
+        <v>525.9299999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>512.2407300748195</v>
+        <v>26.22</v>
       </c>
       <c r="T5" t="n">
-        <v>40.43378768232011</v>
+        <v>521.58</v>
       </c>
       <c r="U5" t="n">
-        <v>511.0721135366621</v>
+        <v>35.56</v>
       </c>
       <c r="V5" t="n">
-        <v>43.41974348519667</v>
+        <v>522.92</v>
       </c>
       <c r="W5" t="n">
-        <v>513.8103737896764</v>
+        <v>33.69</v>
       </c>
       <c r="X5" t="n">
-        <v>44.29519728039378</v>
+        <v>513.67</v>
       </c>
       <c r="Y5" t="n">
-        <v>514.9280417523305</v>
+        <v>34.05</v>
       </c>
       <c r="Z5" t="n">
-        <v>44.43516322323585</v>
+        <v>512.97</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>41.09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>512.61</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>40.98</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>512.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>38.21</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>513.38</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>38.43</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>515.23</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>40.7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>509.775</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>510.5</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>511.3</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>511.07</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>510.375</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>509.8071428571429</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>510.2</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>510.8222222222222</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>512.3200000000001</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>73.17461564641116</v>
+        <v>505.325</v>
       </c>
       <c r="AT5" t="n">
-        <v>64.605082359414</v>
+        <v>509.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>59.73993639099393</v>
+        <v>511.2625</v>
       </c>
       <c r="AV5" t="n">
-        <v>56.72605309732028</v>
+        <v>512.1900000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>54.38383070055535</v>
+        <v>511.9666666666666</v>
       </c>
       <c r="AX5" t="n">
-        <v>52.58162313809583</v>
+        <v>511.7214285714286</v>
       </c>
       <c r="AY5" t="n">
-        <v>51.16404987879673</v>
+        <v>511.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>51.66302735091826</v>
+        <v>511.5611111111111</v>
       </c>
       <c r="BA5" t="n">
-        <v>52.14400828474927</v>
+        <v>511.79</v>
       </c>
       <c r="BB5" t="n">
-        <v>332</v>
+        <v>70.48701564827383</v>
       </c>
       <c r="BC5" t="n">
-        <v>332</v>
+        <v>61.71823069401779</v>
       </c>
       <c r="BD5" t="n">
-        <v>332</v>
+        <v>57.46841387884304</v>
       </c>
       <c r="BE5" t="n">
-        <v>332</v>
+        <v>53.88630531034764</v>
       </c>
       <c r="BF5" t="n">
-        <v>332</v>
+        <v>51.34977009577442</v>
       </c>
       <c r="BG5" t="n">
-        <v>332</v>
+        <v>50.27127379913657</v>
       </c>
       <c r="BH5" t="n">
-        <v>332</v>
+        <v>49.23796807342886</v>
       </c>
       <c r="BI5" t="n">
-        <v>332</v>
+        <v>48.03519125355318</v>
       </c>
       <c r="BJ5" t="n">
-        <v>332</v>
+        <v>47.31443648612968</v>
       </c>
       <c r="BK5" t="n">
-        <v>669</v>
+        <v>334</v>
       </c>
       <c r="BL5" t="n">
-        <v>669</v>
+        <v>334</v>
       </c>
       <c r="BM5" t="n">
-        <v>669</v>
+        <v>334</v>
       </c>
       <c r="BN5" t="n">
-        <v>669</v>
+        <v>334</v>
       </c>
       <c r="BO5" t="n">
-        <v>669</v>
+        <v>334</v>
       </c>
       <c r="BP5" t="n">
-        <v>669</v>
+        <v>334</v>
       </c>
       <c r="BQ5" t="n">
-        <v>669</v>
+        <v>334</v>
       </c>
       <c r="BR5" t="n">
-        <v>669</v>
+        <v>334</v>
       </c>
       <c r="BS5" t="n">
-        <v>669</v>
+        <v>334</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.5</v>
+        <v>669</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.5</v>
+        <v>669</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.46875</v>
+        <v>669</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.525</v>
+        <v>669</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.65</v>
+        <v>669</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.8</v>
+        <v>669</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.9111111111111111</v>
+        <v>669</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.9375</v>
+        <v>669</v>
       </c>
       <c r="CB5" t="n">
-        <v>1</v>
+        <v>669</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0.9032258064516129</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.8918918918918919</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.9069767441860465</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0.9565217391304348</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0.8679245283018868</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.8166666666666667</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>515.23</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>40.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S08_G8_521_42_REL2</t>
+          <t>S05_G8_520_42_REL2</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C6" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D6" t="n">
         <v>42</v>
       </c>
-      <c r="D6" t="n">
-        <v>62.26834692364714</v>
-      </c>
       <c r="E6" t="n">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F6" t="n">
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>519.5435805025413</v>
-      </c>
-      <c r="J6" t="n">
-        <v>63.53782185848426</v>
-      </c>
-      <c r="K6" t="n">
-        <v>517.0609654864816</v>
-      </c>
-      <c r="L6" t="n">
-        <v>64.65255203351357</v>
-      </c>
-      <c r="M6" t="n">
-        <v>515.3804128132429</v>
-      </c>
-      <c r="N6" t="n">
-        <v>53.12379672962371</v>
-      </c>
-      <c r="O6" t="n">
-        <v>506.2759456052285</v>
-      </c>
-      <c r="P6" t="n">
-        <v>57.89406235937685</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>505.6432827474665</v>
-      </c>
       <c r="R6" t="n">
-        <v>57.34842547458465</v>
+        <v>538.25</v>
       </c>
       <c r="S6" t="n">
-        <v>505.5397899704392</v>
+        <v>42.21</v>
       </c>
       <c r="T6" t="n">
-        <v>57.36373672334361</v>
+        <v>534.1799999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>506.7541547191871</v>
+        <v>37.48</v>
       </c>
       <c r="V6" t="n">
-        <v>52.7013024827762</v>
+        <v>530.01</v>
       </c>
       <c r="W6" t="n">
-        <v>507.5820443143509</v>
+        <v>35.9</v>
       </c>
       <c r="X6" t="n">
-        <v>54.64532288305096</v>
+        <v>526.78</v>
       </c>
       <c r="Y6" t="n">
-        <v>512.230615603483</v>
+        <v>31.73</v>
       </c>
       <c r="Z6" t="n">
-        <v>53.01625982571952</v>
+        <v>524.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>32.73</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>525.78</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>36.09</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>525.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>37.07</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>524.46</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>38.43</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>525.54</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>40.72</v>
       </c>
       <c r="AJ6" t="n">
-        <v>519.325</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>517.2166666666667</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>515.775</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>514.04</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>512.25</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>511.2142857142857</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>510.05625</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>508.9944444444445</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>509.14</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>100.0848109105473</v>
+        <v>513.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>92.36108337510025</v>
+        <v>517.75</v>
       </c>
       <c r="AU6" t="n">
-        <v>87.97271949303375</v>
+        <v>520.7125</v>
       </c>
       <c r="AV6" t="n">
-        <v>83.51010956764456</v>
+        <v>521.6</v>
       </c>
       <c r="AW6" t="n">
-        <v>80.19520455322333</v>
+        <v>519.2833333333333</v>
       </c>
       <c r="AX6" t="n">
-        <v>77.71778484769527</v>
+        <v>518.6857142857143</v>
       </c>
       <c r="AY6" t="n">
-        <v>75.19476767659768</v>
+        <v>519.225</v>
       </c>
       <c r="AZ6" t="n">
-        <v>72.74097860996787</v>
+        <v>520.4333333333333</v>
       </c>
       <c r="BA6" t="n">
-        <v>70.89675874114415</v>
+        <v>522.215</v>
       </c>
       <c r="BB6" t="n">
-        <v>329</v>
+        <v>77.54895228176845</v>
       </c>
       <c r="BC6" t="n">
-        <v>329</v>
+        <v>69.6841983522807</v>
       </c>
       <c r="BD6" t="n">
-        <v>329</v>
+        <v>63.96213601616194</v>
       </c>
       <c r="BE6" t="n">
-        <v>329</v>
+        <v>59.43820320299058</v>
       </c>
       <c r="BF6" t="n">
-        <v>329</v>
+        <v>56.66071292252586</v>
       </c>
       <c r="BG6" t="n">
-        <v>329</v>
+        <v>54.47084222830802</v>
       </c>
       <c r="BH6" t="n">
-        <v>329</v>
+        <v>52.50070832855496</v>
       </c>
       <c r="BI6" t="n">
-        <v>329</v>
+        <v>52.38745608975068</v>
       </c>
       <c r="BJ6" t="n">
-        <v>329</v>
+        <v>53.57302282865883</v>
       </c>
       <c r="BK6" t="n">
-        <v>675</v>
+        <v>320</v>
       </c>
       <c r="BL6" t="n">
-        <v>675</v>
+        <v>320</v>
       </c>
       <c r="BM6" t="n">
-        <v>675</v>
+        <v>320</v>
       </c>
       <c r="BN6" t="n">
-        <v>675</v>
+        <v>320</v>
       </c>
       <c r="BO6" t="n">
-        <v>675</v>
+        <v>320</v>
       </c>
       <c r="BP6" t="n">
-        <v>675</v>
+        <v>320</v>
       </c>
       <c r="BQ6" t="n">
-        <v>675</v>
+        <v>320</v>
       </c>
       <c r="BR6" t="n">
-        <v>675</v>
+        <v>320</v>
       </c>
       <c r="BS6" t="n">
-        <v>675</v>
+        <v>320</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.5882352941176471</v>
+        <v>669</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.8695652173913043</v>
+        <v>669</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.8275862068965517</v>
+        <v>669</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.631578947368421</v>
+        <v>669</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.5319148936170213</v>
+        <v>669</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.5961538461538461</v>
+        <v>669</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.5714285714285714</v>
+        <v>669</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.5964912280701754</v>
+        <v>669</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.5483870967741935</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.6857142857142857</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.9722222222222222</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>525.54</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>40.72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S07_G8_521_39_REL2</t>
+          <t>S06_G8_518_40_REL2</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C7" t="n">
-        <v>39</v>
+        <v>59.30318754633062</v>
       </c>
       <c r="D7" t="n">
-        <v>57.82060785767235</v>
+        <v>40</v>
       </c>
       <c r="E7" t="n">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F7" t="n">
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>547.8386198979277</v>
-      </c>
-      <c r="J7" t="n">
-        <v>30.97054988827753</v>
-      </c>
-      <c r="K7" t="n">
-        <v>545.9288116323514</v>
-      </c>
-      <c r="L7" t="n">
-        <v>31.24847857944629</v>
-      </c>
-      <c r="M7" t="n">
-        <v>536.091817581189</v>
-      </c>
-      <c r="N7" t="n">
-        <v>35.857291965149</v>
-      </c>
-      <c r="O7" t="n">
-        <v>544.8138114270787</v>
-      </c>
-      <c r="P7" t="n">
-        <v>35.99767587213221</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>539.2080437530507</v>
-      </c>
       <c r="R7" t="n">
-        <v>37.94921175671553</v>
+        <v>524.77</v>
       </c>
       <c r="S7" t="n">
-        <v>537.8089251225373</v>
+        <v>20.92</v>
       </c>
       <c r="T7" t="n">
-        <v>38.62749440634983</v>
+        <v>532.29</v>
       </c>
       <c r="U7" t="n">
-        <v>532.8712483974931</v>
+        <v>30.55</v>
       </c>
       <c r="V7" t="n">
-        <v>40.57136173312911</v>
+        <v>520.65</v>
       </c>
       <c r="W7" t="n">
-        <v>532.7213715884058</v>
+        <v>32.55</v>
       </c>
       <c r="X7" t="n">
-        <v>42.59559401092994</v>
+        <v>525.49</v>
       </c>
       <c r="Y7" t="n">
-        <v>529.1896524948755</v>
+        <v>38.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>43.23909005284459</v>
+        <v>530.45</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>37.89</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>528.3099999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>40.47</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>527.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>46.13</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>529.36</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>46.04</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>529.9</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>46.74</v>
       </c>
       <c r="AJ7" t="n">
-        <v>518.65</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>526.35</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>527.9875</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>529.28</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>528.975</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>528.0571428571428</v>
+        <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>526.86875</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>526.1388888888889</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>524.4349999999999</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>75.98636390826975</v>
+        <v>507.725</v>
       </c>
       <c r="AT7" t="n">
-        <v>69.74807643703637</v>
+        <v>512.8666666666667</v>
       </c>
       <c r="AU7" t="n">
-        <v>64.81116681367494</v>
+        <v>515.6875</v>
       </c>
       <c r="AV7" t="n">
-        <v>61.5322809588593</v>
+        <v>517.85</v>
       </c>
       <c r="AW7" t="n">
-        <v>58.52427736988015</v>
+        <v>521.1</v>
       </c>
       <c r="AX7" t="n">
-        <v>57.03129108888651</v>
+        <v>523.4928571428571</v>
       </c>
       <c r="AY7" t="n">
-        <v>57.15692454495343</v>
+        <v>526.4375</v>
       </c>
       <c r="AZ7" t="n">
-        <v>57.10699158294298</v>
+        <v>527.8722222222223</v>
       </c>
       <c r="BA7" t="n">
-        <v>57.76439885431164</v>
+        <v>528.09</v>
       </c>
       <c r="BB7" t="n">
-        <v>343</v>
+        <v>71.18356112895729</v>
       </c>
       <c r="BC7" t="n">
-        <v>343</v>
+        <v>62.14404414119041</v>
       </c>
       <c r="BD7" t="n">
-        <v>343</v>
+        <v>57.82270180257924</v>
       </c>
       <c r="BE7" t="n">
-        <v>343</v>
+        <v>56.29109609876149</v>
       </c>
       <c r="BF7" t="n">
-        <v>343</v>
+        <v>56.9506218871518</v>
       </c>
       <c r="BG7" t="n">
-        <v>343</v>
+        <v>57.44742894017742</v>
       </c>
       <c r="BH7" t="n">
-        <v>343</v>
+        <v>59.10305485971093</v>
       </c>
       <c r="BI7" t="n">
-        <v>343</v>
+        <v>60.1590512775699</v>
       </c>
       <c r="BJ7" t="n">
-        <v>343</v>
+        <v>59.79474809713642</v>
       </c>
       <c r="BK7" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BL7" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BM7" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BN7" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BO7" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BP7" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BQ7" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BR7" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BS7" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.7142857142857143</v>
+        <v>669</v>
       </c>
       <c r="BU7" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="BV7" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.9090909090909091</v>
+        <v>669</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.92</v>
+        <v>669</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.7666666666666667</v>
+        <v>669</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.7272727272727273</v>
+        <v>669</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.8333333333333334</v>
+        <v>669</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.8333333333333334</v>
+        <v>669</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.8709677419354839</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.6279069767441861</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>529.9</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>46.74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S06_G8_518_40_REL2</t>
+          <t>S07_G8_521_39_REL2</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C8" t="n">
-        <v>40</v>
+        <v>57.82060785767235</v>
       </c>
       <c r="D8" t="n">
-        <v>59.30318754633062</v>
+        <v>39</v>
       </c>
       <c r="E8" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="F8" t="n">
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>81</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>524.7707738287218</v>
-      </c>
-      <c r="J8" t="n">
-        <v>20.92226578354998</v>
-      </c>
-      <c r="K8" t="n">
-        <v>532.2933665523284</v>
-      </c>
-      <c r="L8" t="n">
-        <v>30.54952094147248</v>
-      </c>
-      <c r="M8" t="n">
-        <v>520.6542057777439</v>
-      </c>
-      <c r="N8" t="n">
-        <v>32.55403273138933</v>
-      </c>
-      <c r="O8" t="n">
-        <v>525.4891867260322</v>
-      </c>
-      <c r="P8" t="n">
-        <v>38.40285455721506</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>530.447647094514</v>
-      </c>
       <c r="R8" t="n">
-        <v>37.88558985324294</v>
+        <v>547.84</v>
       </c>
       <c r="S8" t="n">
-        <v>528.3141095082043</v>
+        <v>30.97</v>
       </c>
       <c r="T8" t="n">
-        <v>40.47087797224701</v>
+        <v>545.9299999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>527.4969687429576</v>
+        <v>31.25</v>
       </c>
       <c r="V8" t="n">
-        <v>46.12928147080507</v>
+        <v>536.09</v>
       </c>
       <c r="W8" t="n">
-        <v>529.3641757770154</v>
+        <v>35.86</v>
       </c>
       <c r="X8" t="n">
-        <v>46.03737826246804</v>
+        <v>544.8099999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>529.9047261798332</v>
+        <v>36</v>
       </c>
       <c r="Z8" t="n">
-        <v>46.73697562203103</v>
+        <v>539.21</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>37.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>537.8099999999999</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>38.63</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>532.87</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>40.57</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>532.72</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>42.6</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>529.1900000000001</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>43.24</v>
       </c>
       <c r="AJ8" t="n">
-        <v>507.725</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>512.8666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>515.6875</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>517.85</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>521.1</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>523.4928571428571</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>526.4375</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>527.8722222222223</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>528.09</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>71.18356112895729</v>
+        <v>518.65</v>
       </c>
       <c r="AT8" t="n">
-        <v>62.14404414119041</v>
+        <v>526.35</v>
       </c>
       <c r="AU8" t="n">
-        <v>57.82270180257924</v>
+        <v>527.9875</v>
       </c>
       <c r="AV8" t="n">
-        <v>56.29109609876149</v>
+        <v>529.28</v>
       </c>
       <c r="AW8" t="n">
-        <v>56.9506218871518</v>
+        <v>528.975</v>
       </c>
       <c r="AX8" t="n">
-        <v>57.44742894017742</v>
+        <v>528.0571428571428</v>
       </c>
       <c r="AY8" t="n">
-        <v>59.10305485971093</v>
+        <v>526.86875</v>
       </c>
       <c r="AZ8" t="n">
-        <v>60.1590512775699</v>
+        <v>526.1388888888889</v>
       </c>
       <c r="BA8" t="n">
-        <v>59.79474809713642</v>
+        <v>524.4349999999999</v>
       </c>
       <c r="BB8" t="n">
-        <v>329</v>
+        <v>75.98636390826975</v>
       </c>
       <c r="BC8" t="n">
-        <v>329</v>
+        <v>69.74807643703637</v>
       </c>
       <c r="BD8" t="n">
-        <v>329</v>
+        <v>64.81116681367494</v>
       </c>
       <c r="BE8" t="n">
-        <v>329</v>
+        <v>61.5322809588593</v>
       </c>
       <c r="BF8" t="n">
-        <v>329</v>
+        <v>58.52427736988015</v>
       </c>
       <c r="BG8" t="n">
-        <v>329</v>
+        <v>57.03129108888651</v>
       </c>
       <c r="BH8" t="n">
-        <v>329</v>
+        <v>57.15692454495343</v>
       </c>
       <c r="BI8" t="n">
-        <v>329</v>
+        <v>57.10699158294298</v>
       </c>
       <c r="BJ8" t="n">
-        <v>329</v>
+        <v>57.76439885431164</v>
       </c>
       <c r="BK8" t="n">
-        <v>669</v>
+        <v>343</v>
       </c>
       <c r="BL8" t="n">
-        <v>669</v>
+        <v>343</v>
       </c>
       <c r="BM8" t="n">
-        <v>669</v>
+        <v>343</v>
       </c>
       <c r="BN8" t="n">
-        <v>669</v>
+        <v>343</v>
       </c>
       <c r="BO8" t="n">
-        <v>669</v>
+        <v>343</v>
       </c>
       <c r="BP8" t="n">
-        <v>669</v>
+        <v>343</v>
       </c>
       <c r="BQ8" t="n">
-        <v>669</v>
+        <v>343</v>
       </c>
       <c r="BR8" t="n">
-        <v>669</v>
+        <v>343</v>
       </c>
       <c r="BS8" t="n">
-        <v>669</v>
+        <v>343</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.8</v>
+        <v>669</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.6666666666666666</v>
+        <v>669</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.6</v>
+        <v>669</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.7777777777777778</v>
+        <v>669</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.9629629629629629</v>
+        <v>669</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.8709677419354839</v>
+        <v>669</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.75</v>
+        <v>669</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.6279069767441861</v>
+        <v>669</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.5625</v>
+        <v>669</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0.7666666666666667</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>529.1900000000001</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>43.24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S05_G8_520_42_REL2</t>
+          <t>S08_G8_521_42_REL2</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C9" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D9" t="n">
         <v>42</v>
       </c>
-      <c r="D9" t="n">
-        <v>62.26834692364714</v>
-      </c>
       <c r="E9" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F9" t="n">
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>82.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>538.2478646230846</v>
-      </c>
-      <c r="J9" t="n">
-        <v>42.21474837507368</v>
-      </c>
-      <c r="K9" t="n">
-        <v>534.1780479902254</v>
-      </c>
-      <c r="L9" t="n">
-        <v>37.47946433904508</v>
-      </c>
-      <c r="M9" t="n">
-        <v>530.0066355626175</v>
-      </c>
-      <c r="N9" t="n">
-        <v>35.89718017679525</v>
-      </c>
-      <c r="O9" t="n">
-        <v>526.7829769206288</v>
-      </c>
-      <c r="P9" t="n">
-        <v>31.73305390055334</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>524.496763671841</v>
-      </c>
       <c r="R9" t="n">
-        <v>32.7297418234777</v>
+        <v>519.54</v>
       </c>
       <c r="S9" t="n">
-        <v>525.7761624713673</v>
+        <v>63.54</v>
       </c>
       <c r="T9" t="n">
-        <v>36.08908745757684</v>
+        <v>517.0599999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>525.1979721455849</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>37.07066034029862</v>
+        <v>515.38</v>
       </c>
       <c r="W9" t="n">
-        <v>524.4610335815402</v>
+        <v>53.12</v>
       </c>
       <c r="X9" t="n">
-        <v>38.42692308887727</v>
+        <v>506.28</v>
       </c>
       <c r="Y9" t="n">
-        <v>525.5356272253566</v>
+        <v>57.89</v>
       </c>
       <c r="Z9" t="n">
-        <v>40.71931685182432</v>
+        <v>505.64</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>57.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>505.54</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>57.36</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>506.75</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>52.7</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>507.58</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>54.65</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>512.23</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>53.02</v>
       </c>
       <c r="AJ9" t="n">
-        <v>513.6</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>517.75</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>520.7125</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>521.6</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>519.2833333333333</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>518.6857142857143</v>
+        <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>519.225</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>520.4333333333333</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>522.215</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>77.54895228176845</v>
+        <v>519.325</v>
       </c>
       <c r="AT9" t="n">
-        <v>69.6841983522807</v>
+        <v>517.2166666666667</v>
       </c>
       <c r="AU9" t="n">
-        <v>63.96213601616194</v>
+        <v>515.775</v>
       </c>
       <c r="AV9" t="n">
-        <v>59.43820320299058</v>
+        <v>514.04</v>
       </c>
       <c r="AW9" t="n">
-        <v>56.66071292252586</v>
+        <v>512.25</v>
       </c>
       <c r="AX9" t="n">
-        <v>54.47084222830802</v>
+        <v>511.2142857142857</v>
       </c>
       <c r="AY9" t="n">
-        <v>52.50070832855496</v>
+        <v>510.05625</v>
       </c>
       <c r="AZ9" t="n">
-        <v>52.38745608975068</v>
+        <v>508.9944444444445</v>
       </c>
       <c r="BA9" t="n">
-        <v>53.57302282865883</v>
+        <v>509.14</v>
       </c>
       <c r="BB9" t="n">
-        <v>320</v>
+        <v>100.0848109105473</v>
       </c>
       <c r="BC9" t="n">
-        <v>320</v>
+        <v>92.36108337510025</v>
       </c>
       <c r="BD9" t="n">
-        <v>320</v>
+        <v>87.97271949303375</v>
       </c>
       <c r="BE9" t="n">
-        <v>320</v>
+        <v>83.51010956764456</v>
       </c>
       <c r="BF9" t="n">
-        <v>320</v>
+        <v>80.19520455322333</v>
       </c>
       <c r="BG9" t="n">
-        <v>320</v>
+        <v>77.71778484769527</v>
       </c>
       <c r="BH9" t="n">
-        <v>320</v>
+        <v>75.19476767659768</v>
       </c>
       <c r="BI9" t="n">
-        <v>320</v>
+        <v>72.74097860996787</v>
       </c>
       <c r="BJ9" t="n">
-        <v>320</v>
+        <v>70.89675874114415</v>
       </c>
       <c r="BK9" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BL9" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BM9" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BN9" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BO9" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BP9" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BQ9" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BR9" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BS9" t="n">
-        <v>669</v>
+        <v>329</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.75</v>
+        <v>675</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.6190476190476191</v>
+        <v>675</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.5483870967741935</v>
+        <v>675</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.6857142857142857</v>
+        <v>675</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.8</v>
+        <v>675</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.8857142857142857</v>
+        <v>675</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.9722222222222222</v>
+        <v>675</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.8333333333333334</v>
+        <v>675</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.7777777777777778</v>
+        <v>675</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0.8275862068965517</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.5319148936170213</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.5961538461538461</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0.5964912280701754</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>512.23</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>53.02</v>
       </c>
     </row>
     <row r="10">
@@ -2808,10 +3127,10 @@
         <v>518</v>
       </c>
       <c r="C10" t="n">
+        <v>60.78576723498888</v>
+      </c>
+      <c r="D10" t="n">
         <v>41</v>
-      </c>
-      <c r="D10" t="n">
-        <v>60.78576723498888</v>
       </c>
       <c r="E10" t="n">
         <v>518</v>
@@ -2820,474 +3139,540 @@
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>81.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>551.161835983526</v>
-      </c>
-      <c r="J10" t="n">
-        <v>31.80981578443576</v>
-      </c>
-      <c r="K10" t="n">
-        <v>539.8453622612074</v>
-      </c>
-      <c r="L10" t="n">
-        <v>41.12335771260021</v>
-      </c>
-      <c r="M10" t="n">
-        <v>535.8122992118045</v>
-      </c>
-      <c r="N10" t="n">
-        <v>35.51973366676026</v>
-      </c>
-      <c r="O10" t="n">
-        <v>526.5970529634775</v>
-      </c>
-      <c r="P10" t="n">
-        <v>41.24992761788405</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>525.3960013974323</v>
-      </c>
       <c r="R10" t="n">
-        <v>37.91235280260069</v>
+        <v>551.16</v>
       </c>
       <c r="S10" t="n">
-        <v>532.6089090828317</v>
+        <v>31.81</v>
       </c>
       <c r="T10" t="n">
-        <v>37.65947954284604</v>
+        <v>539.85</v>
       </c>
       <c r="U10" t="n">
-        <v>526.6932051265177</v>
+        <v>41.12</v>
       </c>
       <c r="V10" t="n">
-        <v>39.04940051491499</v>
+        <v>535.8099999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>524.4266861416704</v>
+        <v>35.52</v>
       </c>
       <c r="X10" t="n">
-        <v>38.22066359954734</v>
+        <v>526.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>526.1616344927651</v>
+        <v>41.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>38.8696590125635</v>
+        <v>525.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>37.91</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>532.61</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>37.66</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>526.6900000000001</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>39.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>524.4299999999999</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>38.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>526.16</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>38.87</v>
       </c>
       <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
         <v>521.15</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AT10" t="n">
         <v>526.6166666666667</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AU10" t="n">
         <v>528.5375</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AV10" t="n">
         <v>525.4299999999999</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AW10" t="n">
         <v>522.2833333333333</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AX10" t="n">
         <v>520.5428571428571</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AY10" t="n">
         <v>519.44375</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AZ10" t="n">
         <v>517.3722222222223</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="BA10" t="n">
         <v>516.22</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="BB10" t="n">
         <v>79.28794044493777</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="BC10" t="n">
         <v>70.21184412587064</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="BD10" t="n">
         <v>65.29432282940071</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="BE10" t="n">
         <v>64.8893296313038</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="BF10" t="n">
         <v>63.51918126746352</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="BG10" t="n">
         <v>60.98681021670311</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="BH10" t="n">
         <v>59.27201562236178</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BI10" t="n">
         <v>57.78456450525286</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BJ10" t="n">
         <v>55.8739796327414</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BK10" t="n">
         <v>327</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BL10" t="n">
         <v>327</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BM10" t="n">
         <v>327</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BN10" t="n">
         <v>327</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BO10" t="n">
         <v>327</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BP10" t="n">
         <v>327</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BQ10" t="n">
         <v>327</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BR10" t="n">
         <v>327</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BS10" t="n">
         <v>327</v>
       </c>
-      <c r="BK10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>669</v>
-      </c>
       <c r="BT10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC10" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BU10" t="n">
+      <c r="CD10" t="n">
         <v>0.8</v>
       </c>
-      <c r="BV10" t="n">
+      <c r="CE10" t="n">
         <v>0.76</v>
       </c>
-      <c r="BW10" t="n">
+      <c r="CF10" t="n">
         <v>0.5428571428571428</v>
       </c>
-      <c r="BX10" t="n">
+      <c r="CG10" t="n">
         <v>0.5</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="CH10" t="n">
         <v>0.5263157894736842</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="CI10" t="n">
         <v>0.5853658536585366</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CJ10" t="n">
         <v>0.6829268292682927</v>
       </c>
-      <c r="CB10" t="n">
+      <c r="CK10" t="n">
         <v>0.7560975609756098</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>526.16</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>38.87</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S12_G8_518_40_REL2</t>
+          <t>S10_G8_520_42_REL2</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C11" t="n">
-        <v>40</v>
+        <v>62.26834692364714</v>
       </c>
       <c r="D11" t="n">
-        <v>59.30318754633062</v>
+        <v>42</v>
       </c>
       <c r="E11" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="F11" t="n">
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>81</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>523.8662546691738</v>
-      </c>
-      <c r="J11" t="n">
-        <v>64.17592265217388</v>
-      </c>
-      <c r="K11" t="n">
-        <v>526.643385938511</v>
-      </c>
-      <c r="L11" t="n">
-        <v>54.88083360177757</v>
-      </c>
-      <c r="M11" t="n">
-        <v>529.2952153109804</v>
-      </c>
-      <c r="N11" t="n">
-        <v>46.08485115516544</v>
-      </c>
-      <c r="O11" t="n">
-        <v>524.3390237717392</v>
-      </c>
-      <c r="P11" t="n">
-        <v>58.75830819009674</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>528.4004777371305</v>
-      </c>
       <c r="R11" t="n">
-        <v>55.40641266843362</v>
+        <v>533.5</v>
       </c>
       <c r="S11" t="n">
-        <v>524.051173181964</v>
+        <v>46.62</v>
       </c>
       <c r="T11" t="n">
-        <v>53.1756444974428</v>
+        <v>549.4299999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>521.0556040221002</v>
+        <v>50.5</v>
       </c>
       <c r="V11" t="n">
-        <v>53.42891935562021</v>
+        <v>546.67</v>
       </c>
       <c r="W11" t="n">
-        <v>522.7799295664066</v>
+        <v>46.53</v>
       </c>
       <c r="X11" t="n">
-        <v>52.57693803193023</v>
+        <v>544.12</v>
       </c>
       <c r="Y11" t="n">
-        <v>522.1446326551896</v>
+        <v>50.72</v>
       </c>
       <c r="Z11" t="n">
-        <v>52.9237355587313</v>
+        <v>536.89</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>48.21</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>526.34</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>48.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>523.09</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>51.8</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>525.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>49.53</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>525.51</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>46.62</v>
       </c>
       <c r="AJ11" t="n">
-        <v>514.575</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>520.5166666666667</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>521.1875</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>520.75</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>520.2666666666667</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>519.6</v>
+        <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>517.75625</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>518.5888888888888</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>518.595</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>86.81672865870955</v>
+        <v>527.325</v>
       </c>
       <c r="AT11" t="n">
-        <v>81.73442597148944</v>
+        <v>530.6166666666667</v>
       </c>
       <c r="AU11" t="n">
-        <v>75.99952199685205</v>
+        <v>532.4375</v>
       </c>
       <c r="AV11" t="n">
-        <v>73.02853894197801</v>
+        <v>533.25</v>
       </c>
       <c r="AW11" t="n">
-        <v>73.91422205653133</v>
+        <v>532.5833333333334</v>
       </c>
       <c r="AX11" t="n">
-        <v>70.96999365929238</v>
+        <v>529.0357142857143</v>
       </c>
       <c r="AY11" t="n">
-        <v>68.25904215514235</v>
+        <v>524.55625</v>
       </c>
       <c r="AZ11" t="n">
-        <v>67.07829495687102</v>
+        <v>520.7722222222222</v>
       </c>
       <c r="BA11" t="n">
-        <v>65.89044676582486</v>
+        <v>519.52</v>
       </c>
       <c r="BB11" t="n">
-        <v>326</v>
+        <v>84.28623478955505</v>
       </c>
       <c r="BC11" t="n">
-        <v>326</v>
+        <v>76.88131365220609</v>
       </c>
       <c r="BD11" t="n">
-        <v>326</v>
+        <v>72.97257083144324</v>
       </c>
       <c r="BE11" t="n">
-        <v>326</v>
+        <v>69.41230078307447</v>
       </c>
       <c r="BF11" t="n">
-        <v>326</v>
+        <v>66.80226834139359</v>
       </c>
       <c r="BG11" t="n">
-        <v>326</v>
+        <v>64.85097319616565</v>
       </c>
       <c r="BH11" t="n">
-        <v>326</v>
+        <v>63.88062566958389</v>
       </c>
       <c r="BI11" t="n">
-        <v>326</v>
+        <v>62.80497419751573</v>
       </c>
       <c r="BJ11" t="n">
-        <v>326</v>
+        <v>62.44084880909291</v>
       </c>
       <c r="BK11" t="n">
-        <v>669</v>
+        <v>337</v>
       </c>
       <c r="BL11" t="n">
-        <v>669</v>
+        <v>337</v>
       </c>
       <c r="BM11" t="n">
-        <v>669</v>
+        <v>337</v>
       </c>
       <c r="BN11" t="n">
-        <v>669</v>
+        <v>337</v>
       </c>
       <c r="BO11" t="n">
-        <v>669</v>
+        <v>337</v>
       </c>
       <c r="BP11" t="n">
-        <v>669</v>
+        <v>337</v>
       </c>
       <c r="BQ11" t="n">
-        <v>669</v>
+        <v>337</v>
       </c>
       <c r="BR11" t="n">
-        <v>669</v>
+        <v>337</v>
       </c>
       <c r="BS11" t="n">
-        <v>669</v>
+        <v>337</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.4285714285714285</v>
+        <v>669</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.875</v>
+        <v>669</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.9523809523809523</v>
+        <v>669</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.9545454545454546</v>
+        <v>669</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.8214285714285714</v>
+        <v>669</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.7931034482758621</v>
+        <v>669</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.6764705882352942</v>
+        <v>669</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.6410256410256411</v>
+        <v>669</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0.5263157894736842</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.5357142857142857</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0.5588235294117647</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.7631578947368421</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.8157894736842105</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.8157894736842105</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0.8157894736842105</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0.8157894736842105</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>525.51</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>46.62</v>
       </c>
     </row>
     <row r="12">
@@ -3300,10 +3685,10 @@
         <v>518</v>
       </c>
       <c r="C12" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D12" t="n">
         <v>42</v>
-      </c>
-      <c r="D12" t="n">
-        <v>62.26834692364714</v>
       </c>
       <c r="E12" t="n">
         <v>518</v>
@@ -3312,474 +3697,540 @@
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>569.0968059255622</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4.879574739471754</v>
-      </c>
-      <c r="K12" t="n">
-        <v>542.0338455643465</v>
-      </c>
-      <c r="L12" t="n">
-        <v>29.28823326508824</v>
-      </c>
-      <c r="M12" t="n">
-        <v>537.2827910717035</v>
-      </c>
-      <c r="N12" t="n">
-        <v>33.21274971593532</v>
-      </c>
-      <c r="O12" t="n">
-        <v>539.4148477315449</v>
-      </c>
-      <c r="P12" t="n">
-        <v>38.31626858289167</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>535.2172399472635</v>
-      </c>
       <c r="R12" t="n">
-        <v>37.56505404481472</v>
+        <v>569.1</v>
       </c>
       <c r="S12" t="n">
-        <v>529.4089826839454</v>
+        <v>4.88</v>
       </c>
       <c r="T12" t="n">
-        <v>42.68919850981699</v>
+        <v>542.03</v>
       </c>
       <c r="U12" t="n">
-        <v>526.5670629173889</v>
+        <v>29.29</v>
       </c>
       <c r="V12" t="n">
-        <v>39.04366805397583</v>
+        <v>537.28</v>
       </c>
       <c r="W12" t="n">
-        <v>528.178556605749</v>
+        <v>33.21</v>
       </c>
       <c r="X12" t="n">
-        <v>39.84511465207451</v>
+        <v>539.41</v>
       </c>
       <c r="Y12" t="n">
-        <v>525.580312265585</v>
+        <v>38.32</v>
       </c>
       <c r="Z12" t="n">
-        <v>45.66518499882534</v>
+        <v>535.22</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>37.57</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>529.41</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>42.69</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>526.5700000000001</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>39.04</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>528.1799999999999</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>39.85</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>525.58</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>45.67</v>
       </c>
       <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
         <v>519.475</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AT12" t="n">
         <v>523.1</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AU12" t="n">
         <v>523.925</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AV12" t="n">
         <v>524.65</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AW12" t="n">
         <v>524.8166666666667</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AX12" t="n">
         <v>523.7285714285714</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AY12" t="n">
         <v>521.34375</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AZ12" t="n">
         <v>518.8944444444444</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="BA12" t="n">
         <v>517.1799999999999</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="BB12" t="n">
         <v>77.96248697290254</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="BC12" t="n">
         <v>69.11963059314867</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="BD12" t="n">
         <v>64.3054770217903</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="BE12" t="n">
         <v>61.54272905876046</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="BF12" t="n">
         <v>59.24693850505883</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="BG12" t="n">
         <v>58.28511729386143</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="BH12" t="n">
         <v>57.8251725975591</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BI12" t="n">
         <v>57.1500459047373</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BJ12" t="n">
         <v>57.22322605376247</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BK12" t="n">
         <v>337</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BL12" t="n">
         <v>337</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BM12" t="n">
         <v>337</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BN12" t="n">
         <v>337</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BO12" t="n">
         <v>337</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BP12" t="n">
         <v>337</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BQ12" t="n">
         <v>337</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BR12" t="n">
         <v>337</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BS12" t="n">
         <v>337</v>
       </c>
-      <c r="BK12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>669</v>
-      </c>
       <c r="BT12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC12" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="BU12" t="n">
+      <c r="CD12" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="BV12" t="n">
+      <c r="CE12" t="n">
         <v>0.5</v>
       </c>
-      <c r="BW12" t="n">
+      <c r="CF12" t="n">
         <v>0.4871794871794872</v>
       </c>
-      <c r="BX12" t="n">
+      <c r="CG12" t="n">
         <v>0.4888888888888889</v>
       </c>
-      <c r="BY12" t="n">
+      <c r="CH12" t="n">
         <v>0.5106382978723404</v>
       </c>
-      <c r="BZ12" t="n">
+      <c r="CI12" t="n">
         <v>0.5106382978723404</v>
       </c>
-      <c r="CA12" t="n">
+      <c r="CJ12" t="n">
         <v>0.5319148936170213</v>
       </c>
-      <c r="CB12" t="n">
+      <c r="CK12" t="n">
         <v>0.6170212765957447</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>525.58</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>45.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S10_G8_520_42_REL2</t>
+          <t>S12_G8_518_40_REL2</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>59.30318754633062</v>
       </c>
       <c r="D13" t="n">
-        <v>62.26834692364714</v>
+        <v>40</v>
       </c>
       <c r="E13" t="n">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F13" t="n">
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>533.496525327702</v>
-      </c>
-      <c r="J13" t="n">
-        <v>46.61554037501683</v>
-      </c>
-      <c r="K13" t="n">
-        <v>549.4326487709213</v>
-      </c>
-      <c r="L13" t="n">
-        <v>50.49666356037721</v>
-      </c>
-      <c r="M13" t="n">
-        <v>546.6672651030426</v>
-      </c>
-      <c r="N13" t="n">
-        <v>46.52610340602507</v>
-      </c>
-      <c r="O13" t="n">
-        <v>544.1193891516936</v>
-      </c>
-      <c r="P13" t="n">
-        <v>50.71652283883721</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>536.8893524076152</v>
-      </c>
       <c r="R13" t="n">
-        <v>48.21100533082814</v>
+        <v>523.87</v>
       </c>
       <c r="S13" t="n">
-        <v>526.3435793564171</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>48.70480273905623</v>
+        <v>526.64</v>
       </c>
       <c r="U13" t="n">
-        <v>523.0931857210757</v>
+        <v>54.88</v>
       </c>
       <c r="V13" t="n">
-        <v>51.79628887968255</v>
+        <v>529.3</v>
       </c>
       <c r="W13" t="n">
-        <v>525.5304780043944</v>
+        <v>46.08</v>
       </c>
       <c r="X13" t="n">
-        <v>49.53202431772353</v>
+        <v>524.34</v>
       </c>
       <c r="Y13" t="n">
-        <v>525.509624630385</v>
+        <v>58.76</v>
       </c>
       <c r="Z13" t="n">
-        <v>46.61870518777387</v>
+        <v>528.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>55.41</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>524.05</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>53.18</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>521.0599999999999</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>53.43</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>522.78</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>52.58</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>522.14</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>52.92</v>
       </c>
       <c r="AJ13" t="n">
-        <v>527.325</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>530.6166666666667</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>532.4375</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>533.25</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>532.5833333333334</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>529.0357142857143</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>524.55625</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>520.7722222222222</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>519.52</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>84.28623478955505</v>
+        <v>514.575</v>
       </c>
       <c r="AT13" t="n">
-        <v>76.88131365220609</v>
+        <v>520.5166666666667</v>
       </c>
       <c r="AU13" t="n">
-        <v>72.97257083144324</v>
+        <v>521.1875</v>
       </c>
       <c r="AV13" t="n">
-        <v>69.41230078307447</v>
+        <v>520.75</v>
       </c>
       <c r="AW13" t="n">
-        <v>66.80226834139359</v>
+        <v>520.2666666666667</v>
       </c>
       <c r="AX13" t="n">
-        <v>64.85097319616565</v>
+        <v>519.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>63.88062566958389</v>
+        <v>517.75625</v>
       </c>
       <c r="AZ13" t="n">
-        <v>62.80497419751573</v>
+        <v>518.5888888888888</v>
       </c>
       <c r="BA13" t="n">
-        <v>62.44084880909291</v>
+        <v>518.595</v>
       </c>
       <c r="BB13" t="n">
-        <v>337</v>
+        <v>86.81672865870955</v>
       </c>
       <c r="BC13" t="n">
-        <v>337</v>
+        <v>81.73442597148944</v>
       </c>
       <c r="BD13" t="n">
-        <v>337</v>
+        <v>75.99952199685205</v>
       </c>
       <c r="BE13" t="n">
-        <v>337</v>
+        <v>73.02853894197801</v>
       </c>
       <c r="BF13" t="n">
-        <v>337</v>
+        <v>73.91422205653133</v>
       </c>
       <c r="BG13" t="n">
-        <v>337</v>
+        <v>70.96999365929238</v>
       </c>
       <c r="BH13" t="n">
-        <v>337</v>
+        <v>68.25904215514235</v>
       </c>
       <c r="BI13" t="n">
-        <v>337</v>
+        <v>67.07829495687102</v>
       </c>
       <c r="BJ13" t="n">
-        <v>337</v>
+        <v>65.89044676582486</v>
       </c>
       <c r="BK13" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BL13" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BM13" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BN13" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BO13" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BP13" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BQ13" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BR13" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BS13" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.5</v>
+        <v>669</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.5263157894736842</v>
+        <v>669</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.5357142857142857</v>
+        <v>669</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.5588235294117647</v>
+        <v>669</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.7631578947368421</v>
+        <v>669</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.8157894736842105</v>
+        <v>669</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.8157894736842105</v>
+        <v>669</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.8157894736842105</v>
+        <v>669</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.8157894736842105</v>
+        <v>669</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.9545454545454546</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.8214285714285714</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0.7931034482758621</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0.6764705882352942</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0.6410256410256411</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>522.14</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>52.92</v>
       </c>
     </row>
     <row r="14">
@@ -3792,10 +4243,10 @@
         <v>519</v>
       </c>
       <c r="C14" t="n">
+        <v>57.82060785767235</v>
+      </c>
+      <c r="D14" t="n">
         <v>39</v>
-      </c>
-      <c r="D14" t="n">
-        <v>57.82060785767235</v>
       </c>
       <c r="E14" t="n">
         <v>519</v>
@@ -3804,720 +4255,819 @@
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>82</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>522.9562743487601</v>
-      </c>
-      <c r="J14" t="n">
-        <v>39.28925166664034</v>
-      </c>
-      <c r="K14" t="n">
-        <v>513.8606287639562</v>
-      </c>
-      <c r="L14" t="n">
-        <v>45.92529472907709</v>
-      </c>
-      <c r="M14" t="n">
-        <v>520.7010158405294</v>
-      </c>
-      <c r="N14" t="n">
-        <v>46.30080296501744</v>
-      </c>
-      <c r="O14" t="n">
-        <v>521.2846159023331</v>
-      </c>
-      <c r="P14" t="n">
-        <v>42.69816285742326</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>516.0844831804395</v>
-      </c>
       <c r="R14" t="n">
-        <v>47.55191567420822</v>
+        <v>522.96</v>
       </c>
       <c r="S14" t="n">
-        <v>518.7683765317336</v>
+        <v>39.29</v>
       </c>
       <c r="T14" t="n">
-        <v>45.24057251647629</v>
+        <v>513.86</v>
       </c>
       <c r="U14" t="n">
-        <v>517.9863514272428</v>
+        <v>45.93</v>
       </c>
       <c r="V14" t="n">
-        <v>47.17065707504442</v>
+        <v>520.7</v>
       </c>
       <c r="W14" t="n">
-        <v>515.2465909079409</v>
+        <v>46.3</v>
       </c>
       <c r="X14" t="n">
-        <v>46.50648839578155</v>
+        <v>521.28</v>
       </c>
       <c r="Y14" t="n">
-        <v>511.9114710715722</v>
+        <v>42.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>45.45051123719634</v>
+        <v>516.08</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>47.55</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>518.77</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>45.24</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>517.99</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>47.17</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>515.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>46.51</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>511.91</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>45.45</v>
       </c>
       <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
         <v>512.2</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AT14" t="n">
         <v>512.15</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AU14" t="n">
         <v>512.8</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AV14" t="n">
         <v>512.75</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AW14" t="n">
         <v>510.6916666666667</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AX14" t="n">
         <v>508.5071428571429</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AY14" t="n">
         <v>508.9</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AZ14" t="n">
         <v>506.6888888888889</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="BA14" t="n">
         <v>505.57</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="BB14" t="n">
         <v>78.43443121486889</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="BC14" t="n">
         <v>70.40047940177679</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="BD14" t="n">
         <v>66.37533427411118</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="BE14" t="n">
         <v>62.60197680584855</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="BF14" t="n">
         <v>63.19662383299355</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="BG14" t="n">
         <v>62.88952858880761</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="BH14" t="n">
         <v>62.95764449215043</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="BI14" t="n">
         <v>63.80746115279491</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BJ14" t="n">
         <v>62.34488832294112</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BK14" t="n">
         <v>341</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BL14" t="n">
         <v>341</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BM14" t="n">
         <v>341</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BN14" t="n">
         <v>341</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BO14" t="n">
         <v>341</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BP14" t="n">
         <v>341</v>
       </c>
-      <c r="BH14" t="n">
+      <c r="BQ14" t="n">
         <v>341</v>
       </c>
-      <c r="BI14" t="n">
+      <c r="BR14" t="n">
         <v>341</v>
       </c>
-      <c r="BJ14" t="n">
+      <c r="BS14" t="n">
         <v>341</v>
       </c>
-      <c r="BK14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>669</v>
-      </c>
       <c r="BT14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC14" t="n">
         <v>0.6</v>
       </c>
-      <c r="BU14" t="n">
+      <c r="CD14" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BV14" t="n">
+      <c r="CE14" t="n">
         <v>0.625</v>
       </c>
-      <c r="BW14" t="n">
+      <c r="CF14" t="n">
         <v>0.7241379310344828</v>
       </c>
-      <c r="BX14" t="n">
+      <c r="CG14" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BY14" t="n">
+      <c r="CH14" t="n">
         <v>0.6470588235294118</v>
       </c>
-      <c r="BZ14" t="n">
+      <c r="CI14" t="n">
         <v>0.7352941176470589</v>
       </c>
-      <c r="CA14" t="n">
+      <c r="CJ14" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="CB14" t="n">
+      <c r="CK14" t="n">
         <v>0.7142857142857143</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>511.91</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>45.45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S15_G8_521_42_REL2</t>
+          <t>S14_G8_520_41_REL2</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>60.78576723498888</v>
       </c>
       <c r="D15" t="n">
-        <v>62.26834692364714</v>
+        <v>41</v>
       </c>
       <c r="E15" t="n">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F15" t="n">
         <v>200</v>
       </c>
       <c r="G15" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>552.591934640306</v>
-      </c>
-      <c r="J15" t="n">
-        <v>12.7206834526124</v>
-      </c>
-      <c r="K15" t="n">
-        <v>545.8963842183525</v>
-      </c>
-      <c r="L15" t="n">
-        <v>35.38725737898123</v>
-      </c>
-      <c r="M15" t="n">
-        <v>538.3463513308282</v>
-      </c>
-      <c r="N15" t="n">
-        <v>49.5056749132346</v>
-      </c>
-      <c r="O15" t="n">
-        <v>528.9951557025651</v>
-      </c>
-      <c r="P15" t="n">
-        <v>48.29302053281555</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>527.641551657494</v>
-      </c>
       <c r="R15" t="n">
-        <v>48.91209619335294</v>
+        <v>499.04</v>
       </c>
       <c r="S15" t="n">
-        <v>521.0990653521466</v>
+        <v>33.59</v>
       </c>
       <c r="T15" t="n">
-        <v>53.75829446913021</v>
+        <v>515.91</v>
       </c>
       <c r="U15" t="n">
-        <v>522.9715954634146</v>
+        <v>28.95</v>
       </c>
       <c r="V15" t="n">
-        <v>51.21236868422866</v>
+        <v>518.89</v>
       </c>
       <c r="W15" t="n">
-        <v>523.5037865178024</v>
+        <v>41.74</v>
       </c>
       <c r="X15" t="n">
-        <v>48.30813493601885</v>
+        <v>517.27</v>
       </c>
       <c r="Y15" t="n">
-        <v>525.5658459218896</v>
+        <v>40.64</v>
       </c>
       <c r="Z15" t="n">
-        <v>47.22130537778759</v>
+        <v>516.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>38.22</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>515.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>36.37</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>519.1</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>41.67</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>521.3</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>44.99</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>521.95</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>46.12</v>
       </c>
       <c r="AJ15" t="n">
-        <v>519.65</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>524.55</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>527.5125</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>527.64</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>526.5916666666667</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>521.8928571428571</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>518.05625</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>515.9611111111111</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>514.98</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>72.77621520799224</v>
+        <v>493.275</v>
       </c>
       <c r="AT15" t="n">
-        <v>65.13023491436216</v>
+        <v>499.35</v>
       </c>
       <c r="AU15" t="n">
-        <v>65.75522674092151</v>
+        <v>506.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>64.30155830149064</v>
+        <v>511.58</v>
       </c>
       <c r="AW15" t="n">
-        <v>62.32448633741174</v>
+        <v>513.2166666666667</v>
       </c>
       <c r="AX15" t="n">
-        <v>62.75390670008083</v>
+        <v>514.1428571428571</v>
       </c>
       <c r="AY15" t="n">
-        <v>65.44026349226827</v>
+        <v>517.4625</v>
       </c>
       <c r="AZ15" t="n">
-        <v>66.03268247103844</v>
+        <v>520.6277777777777</v>
       </c>
       <c r="BA15" t="n">
-        <v>66.00067878438828</v>
+        <v>523.3049999999999</v>
       </c>
       <c r="BB15" t="n">
-        <v>344</v>
+        <v>74.50939118661486</v>
       </c>
       <c r="BC15" t="n">
-        <v>344</v>
+        <v>63.91891347637255</v>
       </c>
       <c r="BD15" t="n">
-        <v>344</v>
+        <v>59.94280607379003</v>
       </c>
       <c r="BE15" t="n">
-        <v>344</v>
+        <v>58.5686229990086</v>
       </c>
       <c r="BF15" t="n">
-        <v>344</v>
+        <v>56.68571003544211</v>
       </c>
       <c r="BG15" t="n">
-        <v>344</v>
+        <v>54.5074793594645</v>
       </c>
       <c r="BH15" t="n">
-        <v>344</v>
+        <v>55.65135751938133</v>
       </c>
       <c r="BI15" t="n">
-        <v>344</v>
+        <v>57.65520411661375</v>
       </c>
       <c r="BJ15" t="n">
-        <v>344</v>
+        <v>59.93906885329468</v>
       </c>
       <c r="BK15" t="n">
-        <v>669</v>
+        <v>325</v>
       </c>
       <c r="BL15" t="n">
-        <v>669</v>
+        <v>325</v>
       </c>
       <c r="BM15" t="n">
-        <v>669</v>
+        <v>325</v>
       </c>
       <c r="BN15" t="n">
-        <v>669</v>
+        <v>325</v>
       </c>
       <c r="BO15" t="n">
-        <v>669</v>
+        <v>325</v>
       </c>
       <c r="BP15" t="n">
-        <v>669</v>
+        <v>325</v>
       </c>
       <c r="BQ15" t="n">
-        <v>669</v>
+        <v>325</v>
       </c>
       <c r="BR15" t="n">
-        <v>669</v>
+        <v>325</v>
       </c>
       <c r="BS15" t="n">
-        <v>669</v>
+        <v>325</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.7777777777777778</v>
+        <v>669</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.9230769230769231</v>
+        <v>669</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.6666666666666666</v>
+        <v>669</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.6521739130434783</v>
+        <v>669</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.7777777777777778</v>
+        <v>669</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.7777777777777778</v>
+        <v>669</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.8888888888888888</v>
+        <v>669</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.9259259259259259</v>
+        <v>669</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0.4117647058823529</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>0.6842105263157895</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0.5909090909090909</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>521.95</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>46.12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S14_G8_520_41_REL2</t>
+          <t>S15_G8_521_42_REL2</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>62.26834692364714</v>
       </c>
       <c r="D16" t="n">
-        <v>60.78576723498888</v>
+        <v>42</v>
       </c>
       <c r="E16" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F16" t="n">
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>81.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>499.0389444462834</v>
-      </c>
-      <c r="J16" t="n">
-        <v>33.59132333736305</v>
-      </c>
-      <c r="K16" t="n">
-        <v>515.9148123352753</v>
-      </c>
-      <c r="L16" t="n">
-        <v>28.94734021909814</v>
-      </c>
-      <c r="M16" t="n">
-        <v>518.8889841321104</v>
-      </c>
-      <c r="N16" t="n">
-        <v>41.73565731505678</v>
-      </c>
-      <c r="O16" t="n">
-        <v>517.2730039624494</v>
-      </c>
-      <c r="P16" t="n">
-        <v>40.63924791559565</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>516.3456604480966</v>
-      </c>
       <c r="R16" t="n">
-        <v>38.21698033912831</v>
+        <v>552.59</v>
       </c>
       <c r="S16" t="n">
-        <v>515.4974440343096</v>
+        <v>12.72</v>
       </c>
       <c r="T16" t="n">
-        <v>36.36998842114925</v>
+        <v>545.9</v>
       </c>
       <c r="U16" t="n">
-        <v>519.1029343341675</v>
+        <v>35.39</v>
       </c>
       <c r="V16" t="n">
-        <v>41.67469555213872</v>
+        <v>538.35</v>
       </c>
       <c r="W16" t="n">
-        <v>521.2999794699924</v>
+        <v>49.51</v>
       </c>
       <c r="X16" t="n">
-        <v>44.99315824232239</v>
+        <v>529</v>
       </c>
       <c r="Y16" t="n">
-        <v>521.946186591225</v>
+        <v>48.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>46.11573858622558</v>
+        <v>527.64</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>48.91</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>521.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>53.76</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>522.97</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>51.21</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>523.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>48.31</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>525.5700000000001</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>47.22</v>
       </c>
       <c r="AJ16" t="n">
-        <v>493.275</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>499.35</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>506.6</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>511.58</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>513.2166666666667</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>514.1428571428571</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>517.4625</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>520.6277777777777</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>523.3049999999999</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>74.50939118661486</v>
+        <v>519.65</v>
       </c>
       <c r="AT16" t="n">
-        <v>63.91891347637255</v>
+        <v>524.55</v>
       </c>
       <c r="AU16" t="n">
-        <v>59.94280607379003</v>
+        <v>527.5125</v>
       </c>
       <c r="AV16" t="n">
-        <v>58.5686229990086</v>
+        <v>527.64</v>
       </c>
       <c r="AW16" t="n">
-        <v>56.68571003544211</v>
+        <v>526.5916666666667</v>
       </c>
       <c r="AX16" t="n">
-        <v>54.5074793594645</v>
+        <v>521.8928571428571</v>
       </c>
       <c r="AY16" t="n">
-        <v>55.65135751938133</v>
+        <v>518.05625</v>
       </c>
       <c r="AZ16" t="n">
-        <v>57.65520411661375</v>
+        <v>515.9611111111111</v>
       </c>
       <c r="BA16" t="n">
-        <v>59.93906885329468</v>
+        <v>514.98</v>
       </c>
       <c r="BB16" t="n">
-        <v>325</v>
+        <v>72.77621520799224</v>
       </c>
       <c r="BC16" t="n">
-        <v>325</v>
+        <v>65.13023491436216</v>
       </c>
       <c r="BD16" t="n">
-        <v>325</v>
+        <v>65.75522674092151</v>
       </c>
       <c r="BE16" t="n">
-        <v>325</v>
+        <v>64.30155830149064</v>
       </c>
       <c r="BF16" t="n">
-        <v>325</v>
+        <v>62.32448633741174</v>
       </c>
       <c r="BG16" t="n">
-        <v>325</v>
+        <v>62.75390670008083</v>
       </c>
       <c r="BH16" t="n">
-        <v>325</v>
+        <v>65.44026349226827</v>
       </c>
       <c r="BI16" t="n">
-        <v>325</v>
+        <v>66.03268247103844</v>
       </c>
       <c r="BJ16" t="n">
-        <v>325</v>
+        <v>66.00067878438828</v>
       </c>
       <c r="BK16" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BL16" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BM16" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BN16" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BO16" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BP16" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BQ16" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BR16" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BS16" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BT16" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.4117647058823529</v>
+        <v>669</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.6842105263157895</v>
+        <v>669</v>
       </c>
       <c r="BW16" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.8636363636363636</v>
+        <v>669</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.9629629629629629</v>
+        <v>669</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.7428571428571429</v>
+        <v>669</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.6341463414634146</v>
+        <v>669</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.5909090909090909</v>
+        <v>669</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0.9259259259259259</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>525.5700000000001</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>47.22</v>
       </c>
     </row>
     <row r="17">
@@ -4530,10 +5080,10 @@
         <v>518</v>
       </c>
       <c r="C17" t="n">
+        <v>60.78576723498888</v>
+      </c>
+      <c r="D17" t="n">
         <v>41</v>
-      </c>
-      <c r="D17" t="n">
-        <v>60.78576723498888</v>
       </c>
       <c r="E17" t="n">
         <v>518</v>
@@ -4542,982 +5092,1114 @@
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>83</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>494.7790909577444</v>
-      </c>
-      <c r="J17" t="n">
-        <v>40.459741186258</v>
-      </c>
-      <c r="K17" t="n">
-        <v>505.2031357675335</v>
-      </c>
-      <c r="L17" t="n">
-        <v>46.96219196658356</v>
-      </c>
-      <c r="M17" t="n">
-        <v>507.6085250844666</v>
-      </c>
-      <c r="N17" t="n">
-        <v>44.47157994163374</v>
-      </c>
-      <c r="O17" t="n">
-        <v>507.7628399424978</v>
-      </c>
-      <c r="P17" t="n">
-        <v>39.985355059365</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>508.646161351747</v>
-      </c>
       <c r="R17" t="n">
-        <v>42.08951976192392</v>
+        <v>494.78</v>
       </c>
       <c r="S17" t="n">
-        <v>510.9930627086075</v>
+        <v>40.46</v>
       </c>
       <c r="T17" t="n">
-        <v>40.92074599451109</v>
+        <v>505.2</v>
       </c>
       <c r="U17" t="n">
-        <v>515.7829083474029</v>
+        <v>46.96</v>
       </c>
       <c r="V17" t="n">
-        <v>42.89426143711576</v>
+        <v>507.61</v>
       </c>
       <c r="W17" t="n">
-        <v>518.6893153040444</v>
+        <v>44.47</v>
       </c>
       <c r="X17" t="n">
-        <v>41.35282605192143</v>
+        <v>507.76</v>
       </c>
       <c r="Y17" t="n">
-        <v>519.3657281257535</v>
+        <v>39.99</v>
       </c>
       <c r="Z17" t="n">
-        <v>44.40374806870495</v>
+        <v>508.65</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>42.09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>510.99</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>40.92</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>515.78</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>42.89</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>518.6900000000001</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>41.35</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>519.37</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>44.4</v>
       </c>
       <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
         <v>493.725</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AT17" t="n">
         <v>495.7166666666666</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AU17" t="n">
         <v>497.4625</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AV17" t="n">
         <v>499.47</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AW17" t="n">
         <v>499.85</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AX17" t="n">
         <v>501.4571428571429</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AY17" t="n">
         <v>504.9875</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AZ17" t="n">
         <v>508.1055555555556</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="BA17" t="n">
         <v>509.91</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="BB17" t="n">
         <v>79.03701269025797</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="BC17" t="n">
         <v>69.90209621717761</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="BD17" t="n">
         <v>65.57304014417817</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="BE17" t="n">
         <v>61.83550032141731</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="BF17" t="n">
         <v>59.47809820990132</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="BG17" t="n">
         <v>58.98515205766029</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="BH17" t="n">
         <v>59.7210167675501</v>
       </c>
-      <c r="AZ17" t="n">
+      <c r="BI17" t="n">
         <v>61.03555404864193</v>
       </c>
-      <c r="BA17" t="n">
+      <c r="BJ17" t="n">
         <v>62.65366629336228</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BK17" t="n">
         <v>320</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BL17" t="n">
         <v>320</v>
       </c>
-      <c r="BD17" t="n">
+      <c r="BM17" t="n">
         <v>320</v>
       </c>
-      <c r="BE17" t="n">
+      <c r="BN17" t="n">
         <v>320</v>
       </c>
-      <c r="BF17" t="n">
+      <c r="BO17" t="n">
         <v>320</v>
       </c>
-      <c r="BG17" t="n">
+      <c r="BP17" t="n">
         <v>320</v>
       </c>
-      <c r="BH17" t="n">
+      <c r="BQ17" t="n">
         <v>320</v>
       </c>
-      <c r="BI17" t="n">
+      <c r="BR17" t="n">
         <v>320</v>
       </c>
-      <c r="BJ17" t="n">
+      <c r="BS17" t="n">
         <v>320</v>
       </c>
-      <c r="BK17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>669</v>
-      </c>
       <c r="BT17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC17" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="BU17" t="n">
+      <c r="CD17" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="BV17" t="n">
+      <c r="CE17" t="n">
         <v>0.8421052631578947</v>
       </c>
-      <c r="BW17" t="n">
+      <c r="CF17" t="n">
         <v>0.6785714285714286</v>
       </c>
-      <c r="BX17" t="n">
+      <c r="CG17" t="n">
         <v>0.6857142857142857</v>
       </c>
-      <c r="BY17" t="n">
+      <c r="CH17" t="n">
         <v>0.6341463414634146</v>
       </c>
-      <c r="BZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA17" t="n">
+      <c r="CI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ17" t="n">
         <v>0.2926829268292683</v>
       </c>
-      <c r="CB17" t="n">
+      <c r="CK17" t="n">
         <v>0.8292682926829268</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>519.37</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>44.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S20_G8_519_42_REL2</t>
+          <t>S17_G8_518_39_REL2</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C18" t="n">
-        <v>42</v>
+        <v>57.82060785767235</v>
       </c>
       <c r="D18" t="n">
-        <v>62.26834692364714</v>
+        <v>39</v>
       </c>
       <c r="E18" t="n">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F18" t="n">
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>82</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>525.1207699602173</v>
-      </c>
-      <c r="J18" t="n">
-        <v>47.01848599184749</v>
-      </c>
-      <c r="K18" t="n">
-        <v>505.8355965659243</v>
-      </c>
-      <c r="L18" t="n">
-        <v>51.36526140153061</v>
-      </c>
-      <c r="M18" t="n">
-        <v>511.0170159268631</v>
-      </c>
-      <c r="N18" t="n">
-        <v>43.6579503350808</v>
-      </c>
-      <c r="O18" t="n">
-        <v>513.0012088345153</v>
-      </c>
-      <c r="P18" t="n">
-        <v>45.39491829119539</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>508.4173980647512</v>
-      </c>
       <c r="R18" t="n">
-        <v>43.86667282678188</v>
+        <v>507.76</v>
       </c>
       <c r="S18" t="n">
-        <v>514.0016133160933</v>
+        <v>46.85</v>
       </c>
       <c r="T18" t="n">
-        <v>45.49232878675713</v>
+        <v>527.4299999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>513.7412661399558</v>
+        <v>39.77</v>
       </c>
       <c r="V18" t="n">
-        <v>42.35744907465598</v>
+        <v>519.4400000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>513.3663488578147</v>
+        <v>40.48</v>
       </c>
       <c r="X18" t="n">
-        <v>42.22481156550579</v>
+        <v>523.3200000000001</v>
       </c>
       <c r="Y18" t="n">
-        <v>514.0984231365572</v>
+        <v>39.04</v>
       </c>
       <c r="Z18" t="n">
-        <v>44.71010625096999</v>
+        <v>513.54</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>40.55</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>514.16</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>43.54</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>513.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>42.18</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>514.6799999999999</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>40.02</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>516.9</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>41.64</v>
       </c>
       <c r="AJ18" t="n">
-        <v>520.05</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>518.1</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>516.4</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>514.6799999999999</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>512.1333333333333</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>511.9285714285714</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>511.7625</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>511.6888888888889</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>512.425</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>85.75078716839863</v>
+        <v>495.625</v>
       </c>
       <c r="AT18" t="n">
-        <v>77.08668281011101</v>
+        <v>503.1166666666667</v>
       </c>
       <c r="AU18" t="n">
-        <v>71.82036619232736</v>
+        <v>507.675</v>
       </c>
       <c r="AV18" t="n">
-        <v>67.71851740846074</v>
+        <v>509.29</v>
       </c>
       <c r="AW18" t="n">
-        <v>65.37710268553934</v>
+        <v>509.55</v>
       </c>
       <c r="AX18" t="n">
-        <v>62.45668703271124</v>
+        <v>507.8428571428572</v>
       </c>
       <c r="AY18" t="n">
-        <v>60.44940937469944</v>
+        <v>506.38125</v>
       </c>
       <c r="AZ18" t="n">
-        <v>58.26513049928547</v>
+        <v>504.9222222222222</v>
       </c>
       <c r="BA18" t="n">
-        <v>56.99898573659009</v>
+        <v>505.815</v>
       </c>
       <c r="BB18" t="n">
-        <v>318</v>
+        <v>89.06646043825926</v>
       </c>
       <c r="BC18" t="n">
-        <v>318</v>
+        <v>77.42805083143676</v>
       </c>
       <c r="BD18" t="n">
-        <v>318</v>
+        <v>70.58147331276105</v>
       </c>
       <c r="BE18" t="n">
-        <v>318</v>
+        <v>65.85777023252457</v>
       </c>
       <c r="BF18" t="n">
-        <v>318</v>
+        <v>62.77152353310111</v>
       </c>
       <c r="BG18" t="n">
-        <v>318</v>
+        <v>61.03596965590646</v>
       </c>
       <c r="BH18" t="n">
-        <v>318</v>
+        <v>59.89906842712581</v>
       </c>
       <c r="BI18" t="n">
-        <v>318</v>
+        <v>58.71138972934142</v>
       </c>
       <c r="BJ18" t="n">
-        <v>318</v>
+        <v>59.61686653120911</v>
       </c>
       <c r="BK18" t="n">
-        <v>669</v>
+        <v>321</v>
       </c>
       <c r="BL18" t="n">
-        <v>669</v>
+        <v>321</v>
       </c>
       <c r="BM18" t="n">
-        <v>669</v>
+        <v>321</v>
       </c>
       <c r="BN18" t="n">
-        <v>669</v>
+        <v>321</v>
       </c>
       <c r="BO18" t="n">
-        <v>669</v>
+        <v>321</v>
       </c>
       <c r="BP18" t="n">
-        <v>669</v>
+        <v>321</v>
       </c>
       <c r="BQ18" t="n">
-        <v>669</v>
+        <v>321</v>
       </c>
       <c r="BR18" t="n">
-        <v>669</v>
+        <v>321</v>
       </c>
       <c r="BS18" t="n">
-        <v>669</v>
+        <v>321</v>
       </c>
       <c r="BT18" t="n">
-        <v>0.1666666666666667</v>
+        <v>669</v>
       </c>
       <c r="BU18" t="n">
-        <v>0.1666666666666667</v>
+        <v>669</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.1428571428571428</v>
+        <v>669</v>
       </c>
       <c r="BW18" t="n">
-        <v>0.125</v>
+        <v>669</v>
       </c>
       <c r="BX18" t="n">
-        <v>0.9565217391304348</v>
+        <v>669</v>
       </c>
       <c r="BY18" t="n">
-        <v>0.8275862068965517</v>
+        <v>669</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0.6756756756756757</v>
+        <v>669</v>
       </c>
       <c r="CA18" t="n">
-        <v>0.7297297297297297</v>
+        <v>669</v>
       </c>
       <c r="CB18" t="n">
-        <v>0.04878048780487805</v>
+        <v>669</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0.4814814814814815</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0.4594594594594595</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0.4782608695652174</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>516.9</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>41.64</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S19_G8_520_39_REL2</t>
+          <t>S18_G8_519_39_REL2</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C19" t="n">
+        <v>57.82060785767235</v>
+      </c>
+      <c r="D19" t="n">
         <v>39</v>
       </c>
-      <c r="D19" t="n">
-        <v>57.82060785767235</v>
-      </c>
       <c r="E19" t="n">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F19" t="n">
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>82.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>520.7139373553724</v>
-      </c>
-      <c r="J19" t="n">
-        <v>35.6984832393344</v>
-      </c>
-      <c r="K19" t="n">
-        <v>512.0746556973338</v>
-      </c>
-      <c r="L19" t="n">
-        <v>38.2728811094074</v>
-      </c>
-      <c r="M19" t="n">
-        <v>517.1768139459418</v>
-      </c>
-      <c r="N19" t="n">
-        <v>40.29483338331527</v>
-      </c>
-      <c r="O19" t="n">
-        <v>519.3904332843366</v>
-      </c>
-      <c r="P19" t="n">
-        <v>38.42755962257024</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>516.7066072824651</v>
-      </c>
       <c r="R19" t="n">
-        <v>40.23888322113126</v>
+        <v>508.07</v>
       </c>
       <c r="S19" t="n">
-        <v>516.8591838785262</v>
+        <v>45.62</v>
       </c>
       <c r="T19" t="n">
-        <v>41.08997122384904</v>
+        <v>510.73</v>
       </c>
       <c r="U19" t="n">
-        <v>518.9244254509799</v>
+        <v>37.96</v>
       </c>
       <c r="V19" t="n">
-        <v>41.57635687643058</v>
+        <v>505.92</v>
       </c>
       <c r="W19" t="n">
-        <v>516.0890982326571</v>
+        <v>36.52</v>
       </c>
       <c r="X19" t="n">
-        <v>42.78421250591085</v>
+        <v>511.87</v>
       </c>
       <c r="Y19" t="n">
-        <v>515.4192575341731</v>
+        <v>36.82</v>
       </c>
       <c r="Z19" t="n">
-        <v>40.53807670766074</v>
+        <v>515.61</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>36.92</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>515.91</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>40.59</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>514.9299999999999</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>41.96</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>513.61</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>43.24</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>510.85</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>43.06</v>
       </c>
       <c r="AJ19" t="n">
-        <v>502.9</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>506.05</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>509.25</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>510.64</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>511.425</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>510.9142857142857</v>
+        <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>510.9625</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>512.6166666666667</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>512.4299999999999</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>83.42175975127832</v>
+        <v>519.15</v>
       </c>
       <c r="AT19" t="n">
-        <v>72.15525506387829</v>
+        <v>515.1</v>
       </c>
       <c r="AU19" t="n">
-        <v>66.14973544920645</v>
+        <v>512.55</v>
       </c>
       <c r="AV19" t="n">
-        <v>62.59401249320897</v>
+        <v>511.21</v>
       </c>
       <c r="AW19" t="n">
-        <v>60.20252797848277</v>
+        <v>511.8583333333333</v>
       </c>
       <c r="AX19" t="n">
-        <v>58.2567575129132</v>
+        <v>514</v>
       </c>
       <c r="AY19" t="n">
-        <v>57.44517902966271</v>
+        <v>514.5125</v>
       </c>
       <c r="AZ19" t="n">
-        <v>57.20589276173099</v>
+        <v>514.1888888888889</v>
       </c>
       <c r="BA19" t="n">
-        <v>55.97146683802382</v>
+        <v>512.71</v>
       </c>
       <c r="BB19" t="n">
-        <v>344</v>
+        <v>98.61631457319828</v>
       </c>
       <c r="BC19" t="n">
-        <v>344</v>
+        <v>82.80754796514627</v>
       </c>
       <c r="BD19" t="n">
-        <v>344</v>
+        <v>73.34846624163316</v>
       </c>
       <c r="BE19" t="n">
-        <v>344</v>
+        <v>67.25225572425062</v>
       </c>
       <c r="BF19" t="n">
-        <v>344</v>
+        <v>63.72300681247097</v>
       </c>
       <c r="BG19" t="n">
-        <v>344</v>
+        <v>62.79934030590722</v>
       </c>
       <c r="BH19" t="n">
-        <v>344</v>
+        <v>63.67043932430497</v>
       </c>
       <c r="BI19" t="n">
-        <v>344</v>
+        <v>65.00485356997831</v>
       </c>
       <c r="BJ19" t="n">
-        <v>344</v>
+        <v>64.76431038774365</v>
       </c>
       <c r="BK19" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BL19" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BM19" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BN19" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BO19" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BP19" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BQ19" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BR19" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BS19" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BT19" t="n">
-        <v>0.4</v>
+        <v>706</v>
       </c>
       <c r="BU19" t="n">
-        <v>0.5833333333333334</v>
+        <v>706</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.8666666666666667</v>
+        <v>706</v>
       </c>
       <c r="BW19" t="n">
+        <v>706</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>706</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>706</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>706</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>706</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>706</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="CE19" t="n">
         <v>0.7826086956521739</v>
       </c>
-      <c r="BX19" t="n">
-        <v>0.7419354838709677</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>0.7714285714285715</v>
-      </c>
-      <c r="BZ19" t="n">
-        <v>0.6585365853658537</v>
-      </c>
-      <c r="CA19" t="n">
-        <v>0.7317073170731707</v>
-      </c>
-      <c r="CB19" t="n">
-        <v>0.8292682926829268</v>
+      <c r="CF19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>510.85</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>43.06</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S17_G8_518_39_REL2</t>
+          <t>S19_G8_520_39_REL2</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C20" t="n">
+        <v>57.82060785767235</v>
+      </c>
+      <c r="D20" t="n">
         <v>39</v>
       </c>
-      <c r="D20" t="n">
-        <v>57.82060785767235</v>
-      </c>
       <c r="E20" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="F20" t="n">
         <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="H20" t="inlineStr">
+        <v>81</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>507.7601177786341</v>
-      </c>
-      <c r="J20" t="n">
-        <v>46.84655669059298</v>
-      </c>
-      <c r="K20" t="n">
-        <v>527.4306086343557</v>
-      </c>
-      <c r="L20" t="n">
-        <v>39.76750188116532</v>
-      </c>
-      <c r="M20" t="n">
-        <v>519.436419760661</v>
-      </c>
-      <c r="N20" t="n">
-        <v>40.48401186405622</v>
-      </c>
-      <c r="O20" t="n">
-        <v>523.3212739248723</v>
-      </c>
-      <c r="P20" t="n">
-        <v>39.04251254747496</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>513.5399151453832</v>
-      </c>
       <c r="R20" t="n">
-        <v>40.54565825885214</v>
+        <v>520.71</v>
       </c>
       <c r="S20" t="n">
-        <v>514.1610091992625</v>
+        <v>35.7</v>
       </c>
       <c r="T20" t="n">
-        <v>43.54496925567683</v>
+        <v>512.0700000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>513.4037097244818</v>
+        <v>38.27</v>
       </c>
       <c r="V20" t="n">
-        <v>42.17516140192362</v>
+        <v>517.1799999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>514.6845515501867</v>
+        <v>40.29</v>
       </c>
       <c r="X20" t="n">
-        <v>40.01747363975128</v>
+        <v>519.39</v>
       </c>
       <c r="Y20" t="n">
-        <v>516.8990160891035</v>
+        <v>38.43</v>
       </c>
       <c r="Z20" t="n">
-        <v>41.64035519708433</v>
+        <v>516.71</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>40.24</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>516.86</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>41.09</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>518.92</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>41.58</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>516.09</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>42.78</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>515.42</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>40.54</v>
       </c>
       <c r="AJ20" t="n">
-        <v>495.625</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>503.1166666666667</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>507.675</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>509.29</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>509.55</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>507.8428571428572</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>506.38125</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>504.9222222222222</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>505.815</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>89.06646043825926</v>
+        <v>502.9</v>
       </c>
       <c r="AT20" t="n">
-        <v>77.42805083143676</v>
+        <v>506.05</v>
       </c>
       <c r="AU20" t="n">
-        <v>70.58147331276105</v>
+        <v>509.25</v>
       </c>
       <c r="AV20" t="n">
-        <v>65.85777023252457</v>
+        <v>510.64</v>
       </c>
       <c r="AW20" t="n">
-        <v>62.77152353310111</v>
+        <v>511.425</v>
       </c>
       <c r="AX20" t="n">
-        <v>61.03596965590646</v>
+        <v>510.9142857142857</v>
       </c>
       <c r="AY20" t="n">
-        <v>59.89906842712581</v>
+        <v>510.9625</v>
       </c>
       <c r="AZ20" t="n">
-        <v>58.71138972934142</v>
+        <v>512.6166666666667</v>
       </c>
       <c r="BA20" t="n">
-        <v>59.61686653120911</v>
+        <v>512.4299999999999</v>
       </c>
       <c r="BB20" t="n">
-        <v>321</v>
+        <v>83.42175975127832</v>
       </c>
       <c r="BC20" t="n">
-        <v>321</v>
+        <v>72.15525506387829</v>
       </c>
       <c r="BD20" t="n">
-        <v>321</v>
+        <v>66.14973544920645</v>
       </c>
       <c r="BE20" t="n">
-        <v>321</v>
+        <v>62.59401249320897</v>
       </c>
       <c r="BF20" t="n">
-        <v>321</v>
+        <v>60.20252797848277</v>
       </c>
       <c r="BG20" t="n">
-        <v>321</v>
+        <v>58.2567575129132</v>
       </c>
       <c r="BH20" t="n">
-        <v>321</v>
+        <v>57.44517902966271</v>
       </c>
       <c r="BI20" t="n">
-        <v>321</v>
+        <v>57.20589276173099</v>
       </c>
       <c r="BJ20" t="n">
-        <v>321</v>
+        <v>55.97146683802382</v>
       </c>
       <c r="BK20" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BL20" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BM20" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BN20" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BO20" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BP20" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BQ20" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BR20" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BS20" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BT20" t="n">
-        <v>0.5</v>
+        <v>669</v>
       </c>
       <c r="BU20" t="n">
-        <v>0.4705882352941176</v>
+        <v>669</v>
       </c>
       <c r="BV20" t="n">
-        <v>0.4814814814814815</v>
+        <v>669</v>
       </c>
       <c r="BW20" t="n">
-        <v>0.4594594594594595</v>
+        <v>669</v>
       </c>
       <c r="BX20" t="n">
-        <v>0.4782608695652174</v>
+        <v>669</v>
       </c>
       <c r="BY20" t="n">
-        <v>0.4583333333333333</v>
+        <v>669</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0.4615384615384616</v>
+        <v>669</v>
       </c>
       <c r="CA20" t="n">
-        <v>0.4615384615384616</v>
+        <v>669</v>
       </c>
       <c r="CB20" t="n">
-        <v>0.5</v>
+        <v>669</v>
+      </c>
+      <c r="CC20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CD20" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="CE20" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="CF20" t="n">
+        <v>0.7826086956521739</v>
+      </c>
+      <c r="CG20" t="n">
+        <v>0.7419354838709677</v>
+      </c>
+      <c r="CH20" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="CI20" t="n">
+        <v>0.6585365853658537</v>
+      </c>
+      <c r="CJ20" t="n">
+        <v>0.7317073170731707</v>
+      </c>
+      <c r="CK20" t="n">
+        <v>0.8292682926829268</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>515.42</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>40.54</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S18_G8_519_39_REL2</t>
+          <t>S20_G8_519_42_REL2</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>519</v>
       </c>
       <c r="C21" t="n">
-        <v>39</v>
+        <v>62.26834692364714</v>
       </c>
       <c r="D21" t="n">
-        <v>57.82060785767235</v>
+        <v>42</v>
       </c>
       <c r="E21" t="n">
         <v>519</v>
@@ -5526,228 +6208,261 @@
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>508.0703227956474</v>
-      </c>
-      <c r="J21" t="n">
-        <v>45.61947751104779</v>
-      </c>
-      <c r="K21" t="n">
-        <v>510.7311003563908</v>
-      </c>
-      <c r="L21" t="n">
-        <v>37.95694062501357</v>
-      </c>
-      <c r="M21" t="n">
-        <v>505.9189507445673</v>
-      </c>
-      <c r="N21" t="n">
-        <v>36.51863672887428</v>
-      </c>
-      <c r="O21" t="n">
-        <v>511.8725918293658</v>
-      </c>
-      <c r="P21" t="n">
-        <v>36.81528423824881</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>515.6124714285062</v>
-      </c>
       <c r="R21" t="n">
-        <v>36.92081411995497</v>
+        <v>525.12</v>
       </c>
       <c r="S21" t="n">
-        <v>515.9100801169283</v>
+        <v>47.02</v>
       </c>
       <c r="T21" t="n">
-        <v>40.59155063094327</v>
+        <v>505.84</v>
       </c>
       <c r="U21" t="n">
-        <v>514.9324467342029</v>
+        <v>51.37</v>
       </c>
       <c r="V21" t="n">
-        <v>41.95777762979201</v>
+        <v>511.02</v>
       </c>
       <c r="W21" t="n">
-        <v>513.605826875303</v>
+        <v>43.66</v>
       </c>
       <c r="X21" t="n">
-        <v>43.23590198271388</v>
+        <v>513</v>
       </c>
       <c r="Y21" t="n">
-        <v>510.8529094973371</v>
+        <v>45.39</v>
       </c>
       <c r="Z21" t="n">
-        <v>43.06012072982577</v>
+        <v>508.42</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>43.87</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>514</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>45.49</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>513.74</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>42.36</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>513.37</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>42.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>514.1</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>44.71</v>
       </c>
       <c r="AJ21" t="n">
-        <v>519.15</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>515.1</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>512.55</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>511.21</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>511.8583333333333</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>514</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>514.5125</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>514.1888888888889</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>512.71</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>98.61631457319828</v>
+        <v>520.05</v>
       </c>
       <c r="AT21" t="n">
-        <v>82.80754796514627</v>
+        <v>518.1</v>
       </c>
       <c r="AU21" t="n">
-        <v>73.34846624163316</v>
+        <v>516.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>67.25225572425062</v>
+        <v>514.6799999999999</v>
       </c>
       <c r="AW21" t="n">
-        <v>63.72300681247097</v>
+        <v>512.1333333333333</v>
       </c>
       <c r="AX21" t="n">
-        <v>62.79934030590722</v>
+        <v>511.9285714285714</v>
       </c>
       <c r="AY21" t="n">
-        <v>63.67043932430497</v>
+        <v>511.7625</v>
       </c>
       <c r="AZ21" t="n">
-        <v>65.00485356997831</v>
+        <v>511.6888888888889</v>
       </c>
       <c r="BA21" t="n">
-        <v>64.76431038774365</v>
+        <v>512.425</v>
       </c>
       <c r="BB21" t="n">
-        <v>340</v>
+        <v>85.75078716839863</v>
       </c>
       <c r="BC21" t="n">
-        <v>340</v>
+        <v>77.08668281011101</v>
       </c>
       <c r="BD21" t="n">
-        <v>340</v>
+        <v>71.82036619232736</v>
       </c>
       <c r="BE21" t="n">
-        <v>340</v>
+        <v>67.71851740846074</v>
       </c>
       <c r="BF21" t="n">
-        <v>340</v>
+        <v>65.37710268553934</v>
       </c>
       <c r="BG21" t="n">
-        <v>340</v>
+        <v>62.45668703271124</v>
       </c>
       <c r="BH21" t="n">
-        <v>340</v>
+        <v>60.44940937469944</v>
       </c>
       <c r="BI21" t="n">
-        <v>340</v>
+        <v>58.26513049928547</v>
       </c>
       <c r="BJ21" t="n">
-        <v>340</v>
+        <v>56.99898573659009</v>
       </c>
       <c r="BK21" t="n">
-        <v>706</v>
+        <v>318</v>
       </c>
       <c r="BL21" t="n">
-        <v>706</v>
+        <v>318</v>
       </c>
       <c r="BM21" t="n">
-        <v>706</v>
+        <v>318</v>
       </c>
       <c r="BN21" t="n">
-        <v>706</v>
+        <v>318</v>
       </c>
       <c r="BO21" t="n">
-        <v>706</v>
+        <v>318</v>
       </c>
       <c r="BP21" t="n">
-        <v>706</v>
+        <v>318</v>
       </c>
       <c r="BQ21" t="n">
-        <v>706</v>
+        <v>318</v>
       </c>
       <c r="BR21" t="n">
-        <v>706</v>
+        <v>318</v>
       </c>
       <c r="BS21" t="n">
-        <v>706</v>
+        <v>318</v>
       </c>
       <c r="BT21" t="n">
-        <v>0.7142857142857143</v>
+        <v>669</v>
       </c>
       <c r="BU21" t="n">
-        <v>0.3846153846153846</v>
+        <v>669</v>
       </c>
       <c r="BV21" t="n">
-        <v>0.7826086956521739</v>
+        <v>669</v>
       </c>
       <c r="BW21" t="n">
-        <v>0.75</v>
+        <v>669</v>
       </c>
       <c r="BX21" t="n">
-        <v>0.8787878787878788</v>
+        <v>669</v>
       </c>
       <c r="BY21" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="CA21" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="CB21" t="n">
-        <v>1</v>
+        <v>669</v>
+      </c>
+      <c r="CC21" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="CD21" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="CE21" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="CF21" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="CG21" t="n">
+        <v>0.9565217391304348</v>
+      </c>
+      <c r="CH21" t="n">
+        <v>0.8275862068965517</v>
+      </c>
+      <c r="CI21" t="n">
+        <v>0.6756756756756757</v>
+      </c>
+      <c r="CJ21" t="n">
+        <v>0.7297297297297297</v>
+      </c>
+      <c r="CK21" t="n">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>514.1</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>44.71</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>519.55</v>
       </c>
       <c r="C22" t="n">
+        <v>60.04447739065974</v>
+      </c>
+      <c r="D22" t="n">
         <v>40.5</v>
-      </c>
-      <c r="D22" t="n">
-        <v>60.04447739065974</v>
       </c>
       <c r="E22" t="n">
         <v>519.55</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.47825</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>80.47499999999999</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.3325</v>
+      </c>
       <c r="I22" t="n">
-        <v>524.5167529561413</v>
+        <v>2.303</v>
       </c>
       <c r="J22" t="n">
-        <v>37.16509710982426</v>
+        <v>2.3165</v>
       </c>
       <c r="K22" t="n">
-        <v>523.6798703465986</v>
+        <v>2.3355</v>
       </c>
       <c r="L22" t="n">
-        <v>41.3002525102476</v>
+        <v>2.3535</v>
       </c>
       <c r="M22" t="n">
-        <v>523.2690535041769</v>
+        <v>2.378</v>
       </c>
       <c r="N22" t="n">
-        <v>41.48611715995042</v>
+        <v>2.7065</v>
       </c>
       <c r="O22" t="n">
-        <v>522.7384099481342</v>
+        <v>2.518</v>
       </c>
       <c r="P22" t="n">
-        <v>42.62142618199645</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>520.9759991845135</v>
-      </c>
+        <v>2.3865</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>43.443226968131</v>
+        <v>524.5170000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>520.6557351506671</v>
+        <v>37.1655</v>
       </c>
       <c r="T22" t="n">
-        <v>44.68176048849905</v>
+        <v>523.6795</v>
       </c>
       <c r="U22" t="n">
-        <v>519.987376490026</v>
+        <v>41.301</v>
       </c>
       <c r="V22" t="n">
-        <v>44.77922435059961</v>
+        <v>523.2695000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>520.3455498609907</v>
+        <v>41.486</v>
       </c>
       <c r="X22" t="n">
-        <v>44.77703131837047</v>
+        <v>522.7375</v>
       </c>
       <c r="Y22" t="n">
-        <v>520.6307400920658</v>
+        <v>42.6215</v>
       </c>
       <c r="Z22" t="n">
-        <v>45.41597718022409</v>
+        <v>520.9765</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>43.44449999999999</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>520.6559999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>44.681</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>519.9865</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>44.779</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>520.3455000000001</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>44.778</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>520.6310000000001</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>45.41699999999999</v>
       </c>
       <c r="AJ22" t="n">
-        <v>512.3087499999999</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>514.4875</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>516.128125</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>512.3095</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>514.4885000000002</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>516.1279999999999</v>
+      </c>
+      <c r="AV22" t="n">
         <v>516.7875</v>
       </c>
-      <c r="AN22" t="n">
-        <v>516.5354166666665</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>515.9742857142857</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>515.6396875</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>515.3977777777778</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>515.4770000000001</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>81.40856214992237</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>72.34510372821538</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>67.58097445668187</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>64.38211754146849</v>
-      </c>
       <c r="AW22" t="n">
-        <v>62.44045853827632</v>
+        <v>516.5359999999999</v>
       </c>
       <c r="AX22" t="n">
-        <v>61.03581882463942</v>
+        <v>515.9745</v>
       </c>
       <c r="AY22" t="n">
-        <v>60.54600544565368</v>
+        <v>515.6405</v>
       </c>
       <c r="AZ22" t="n">
-        <v>60.22760119032237</v>
+        <v>515.3975</v>
       </c>
       <c r="BA22" t="n">
-        <v>59.95781853495259</v>
+        <v>515.4765</v>
       </c>
       <c r="BB22" t="n">
+        <v>81.40899999999999</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>72.3455</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>67.5805</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>64.38199999999999</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>62.4405</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>61.037</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>60.54650000000002</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>60.2285</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>59.956</v>
+      </c>
+      <c r="BK22" t="n">
         <v>331.35</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>331.35</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>331.35</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>331.35</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>331.35</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>331.35</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>331.35</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>331.35</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>331.35</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BT22" t="n">
         <v>671.45</v>
       </c>
-      <c r="BL22" t="n">
+      <c r="BU22" t="n">
         <v>671.45</v>
       </c>
-      <c r="BM22" t="n">
+      <c r="BV22" t="n">
         <v>671.45</v>
       </c>
-      <c r="BN22" t="n">
+      <c r="BW22" t="n">
         <v>671.45</v>
       </c>
-      <c r="BO22" t="n">
+      <c r="BX22" t="n">
         <v>671.45</v>
       </c>
-      <c r="BP22" t="n">
+      <c r="BY22" t="n">
         <v>671.45</v>
       </c>
-      <c r="BQ22" t="n">
+      <c r="BZ22" t="n">
         <v>671.45</v>
       </c>
-      <c r="BR22" t="n">
+      <c r="CA22" t="n">
         <v>671.45</v>
       </c>
-      <c r="BS22" t="n">
+      <c r="CB22" t="n">
         <v>671.45</v>
       </c>
-      <c r="BT22" t="n">
-        <v>0.5267784992784992</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0.5791121842553731</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0.6751627562062781</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0.6898066490033481</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0.7571808508072155</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0.7581129103054133</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0.6753290572276065</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0.71331150649885</v>
-      </c>
-      <c r="CB22" t="n">
-        <v>0.7088365835755766</v>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>520.6310000000001</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>45.41699999999999</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.316894273021107</v>
       </c>
       <c r="C23" t="n">
+        <v>2.068912423793504</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.395481429848721</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.068912423793504</v>
       </c>
       <c r="E23" t="n">
         <v>1.316894273021107</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01340414311440976</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>1.593366181853275</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2061648548332646</v>
+      </c>
       <c r="I23" t="n">
-        <v>19.54311882756475</v>
+        <v>0.1929575901045288</v>
       </c>
       <c r="J23" t="n">
-        <v>14.56231889475097</v>
+        <v>0.1821010419346474</v>
       </c>
       <c r="K23" t="n">
-        <v>15.09670772117645</v>
+        <v>0.2026787709912568</v>
       </c>
       <c r="L23" t="n">
-        <v>9.722418871496254</v>
+        <v>0.2095176163928641</v>
       </c>
       <c r="M23" t="n">
-        <v>11.11184205150154</v>
+        <v>0.2104531451791335</v>
       </c>
       <c r="N23" t="n">
-        <v>6.601001877195997</v>
+        <v>0.1802125937535121</v>
       </c>
       <c r="O23" t="n">
-        <v>11.00530124304297</v>
+        <v>0.2017711053331681</v>
       </c>
       <c r="P23" t="n">
-        <v>7.585945959583012</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>9.809237343147768</v>
-      </c>
+        <v>0.2246230760981371</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>7.255515938823816</v>
+        <v>19.54353011801308</v>
       </c>
       <c r="S23" t="n">
-        <v>8.417390704680694</v>
+        <v>14.56315772402183</v>
       </c>
       <c r="T23" t="n">
-        <v>6.822984502354074</v>
+        <v>15.09672793931466</v>
       </c>
       <c r="U23" t="n">
-        <v>6.866519934079341</v>
+        <v>9.722114725554421</v>
       </c>
       <c r="V23" t="n">
-        <v>5.477952223481092</v>
+        <v>11.11198900903173</v>
       </c>
       <c r="W23" t="n">
-        <v>6.830997166108232</v>
+        <v>6.600574456658657</v>
       </c>
       <c r="X23" t="n">
-        <v>5.029928713179084</v>
+        <v>11.00522549327794</v>
       </c>
       <c r="Y23" t="n">
-        <v>6.296852570763287</v>
+        <v>7.585158829825794</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.225536154628757</v>
+        <v>9.80968923538034</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>7.255454191593783</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>8.417376388350332</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>6.822998954773634</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>6.867359313984419</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>5.478373654173002</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>6.830673446801723</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>5.030467802877728</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>6.296873827543319</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>4.225861606322369</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9.86044822230394</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>9.379826048275449</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>8.833533479505958</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>9.861848590988355</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>9.380051775752062</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>8.833846155256325</v>
+      </c>
+      <c r="AV23" t="n">
         <v>8.201952190597186</v>
       </c>
-      <c r="AN23" t="n">
-        <v>7.890732625489169</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>7.155221404016361</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>6.310850251788057</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>6.17383556746007</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>6.056599793005274</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>8.198036666898799</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>7.708759914104953</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>7.176174205977634</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>6.711409443041179</v>
-      </c>
       <c r="AW23" t="n">
-        <v>6.695041754589029</v>
+        <v>7.890261419189986</v>
       </c>
       <c r="AX23" t="n">
-        <v>6.417033003237278</v>
+        <v>7.155626034622573</v>
       </c>
       <c r="AY23" t="n">
-        <v>6.194381802700795</v>
+        <v>6.311360246246035</v>
       </c>
       <c r="AZ23" t="n">
-        <v>5.91189255664139</v>
+        <v>6.173541059272728</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.581424693588831</v>
+        <v>6.056691188916162</v>
       </c>
       <c r="BB23" t="n">
+        <v>8.198135795796249</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>7.708607270618447</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>7.175845063016692</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>6.710712253357942</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>6.695679262739046</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>6.417155543007969</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>6.194213152527718</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>5.911068364562054</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>5.58241826489296</v>
+      </c>
+      <c r="BK23" t="n">
         <v>8.424744256621306</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BL23" t="n">
         <v>8.424744256621306</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BM23" t="n">
         <v>8.424744256621306</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BN23" t="n">
         <v>8.424744256621306</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BO23" t="n">
         <v>8.424744256621306</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BP23" t="n">
         <v>8.424744256621306</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BQ23" t="n">
         <v>8.424744256621306</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BR23" t="n">
         <v>8.424744256621306</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BS23" t="n">
         <v>8.424744256621306</v>
       </c>
-      <c r="BK23" t="n">
-        <v>8.338086363820317</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>8.338086363820317</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>8.338086363820317</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>8.338086363820317</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>8.338086363820317</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>8.338086363820317</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>8.338086363820317</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>8.338086363820317</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>8.338086363820317</v>
-      </c>
       <c r="BT23" t="n">
-        <v>0.2714650581448999</v>
+        <v>8.338086363820318</v>
       </c>
       <c r="BU23" t="n">
-        <v>0.248090824808875</v>
+        <v>8.338086363820318</v>
       </c>
       <c r="BV23" t="n">
-        <v>0.2108166052234694</v>
+        <v>8.338086363820318</v>
       </c>
       <c r="BW23" t="n">
-        <v>0.2113183124464207</v>
+        <v>8.338086363820318</v>
       </c>
       <c r="BX23" t="n">
-        <v>0.1553670359698795</v>
+        <v>8.338086363820318</v>
       </c>
       <c r="BY23" t="n">
-        <v>0.1571362384815948</v>
+        <v>8.338086363820318</v>
       </c>
       <c r="BZ23" t="n">
-        <v>0.274208640710916</v>
+        <v>8.338086363820318</v>
       </c>
       <c r="CA23" t="n">
-        <v>0.1708238892648695</v>
+        <v>8.338086363820318</v>
       </c>
       <c r="CB23" t="n">
-        <v>0.2154764444971383</v>
+        <v>8.338086363820318</v>
+      </c>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>6.296873827543319</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>4.225861606322369</v>
       </c>
     </row>
   </sheetData>
